--- a/data/se_data.xlsx
+++ b/data/se_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project -V2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4BE99-DAD7-44DC-9BA5-C35DA05F045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620158CB-7B41-48DF-82BB-F601FC595D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C523A98F-8779-4C7C-A1C9-4783DD7C1920}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="835">
   <si>
     <t>No</t>
   </si>
@@ -1645,13 +1645,943 @@
   </si>
   <si>
     <t>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=Software%20Engineering&amp;highlight=true&amp;returnType=SEARCH&amp;matchPubs=true&amp;pageNumber=41&amp;refinements=ContentType:Conferences&amp;refinements=ContentType:Journals&amp;refinements=ContentType:Early%20Access%20Articles&amp;refinements=ContentType:Courses&amp;ranges=2018_2025_Year&amp;returnFacets=ALL</t>
+  </si>
+  <si>
+    <t>Out of the Day Job: Perspectives of Industry Practitioners in Co-Design and Delivery of Software Engineering Courses</t>
+  </si>
+  <si>
+    <t>Over more than two decades, The University of Glasgow has co-designed and delivered numerous software engineering focused courses with industry partners, covering both technical and discipline specific professional skills. Such collaborations are not unique and many of the benefits are well recognised in the literature. These include enhancing the real-world relevance of curricula, developing student professional networks ahead of graduation and easing recruitment opportunities for employers. However, there is relatively little scholarship on the perspectives of industry practitioners who participate in course design and delivery. This gap is significant, since the effort invested by practitioners is often substantial and may require ongoing support from both the industry partner and academic institution. Understanding the motivations, expectations and experiences of practitioners who engage in course delivery can guide the formation of future partnerships and ensure their long-term sustainability. We begin to address this gap by reporting on the outcomes of a retrospective conducted amongst the practitioner coauthors of this paper, with the academic coauthors acting as facilitators. All coauthors have participated in the recent co-design and delivery of software engineering courses, but we choose to focus explicitly on the perspectives of the practitioners. We report on the themes that emerged from the discussions and our resulting recommendations for future collaborations.</t>
+  </si>
+  <si>
+    <t>A Hierarchical and Evolvable Benchmark for Fine-Grained Code Instruction Following with Multi-Turn Feedback</t>
+  </si>
+  <si>
+    <t>Large language models (LLMs) have advanced significantly in code generation, yet their ability to follow complex programming instructions with layered and diverse constraints remains underexplored. Existing benchmarks often prioritize functional correctness, overlooking the nuanced requirements found in real-world development. We introduce MultiCodeIF, a comprehensive benchmark designed to evaluate instruction-following in code generation across multiple dimensions: constraint type, hierarchical levels, and iterative refinement. Built upon a structured taxonomy of 9 categories and 27 constraint types, MultiCodeIF enables granular assessment of both functional and non-functional instruction adherence. Using an automated pipeline, ConstraGen, we synthesize and evolve 2,021 code tasks sourced from 14 programming languages, supporting multi-turn evaluation through feedback-driven task variants. Empirical evaluation of six state-of-the-art LLMs uncovers substantial performance disparities. The top-performing model, Claude-3-7-Sonnet, achieves 63.0% average constraint satisfaction, while smaller models like Qwen3-1.7B fall to 44.8%. Models perform well on explicit constraints, but struggle with implicit or abstract constraints. Tasks with multiple hierarchical constraints significantly reduce model success rates, from 54.5% in single-level to just 18.8% in multi-level scenarios. However, structured feedback enables progressive improvement: average constraint satisfaction rises from 63.0% to 83.4% over four iterative refinement rounds. MultiCodeIF provides a scalable, constraint-aware, and feedback-sensitive framework to benchmark LLMs under realistic code generation scenarios, bridging the gap between synthetic evaluations and real-world instruction complexity. The full benchmark dataset, evaluation pipeline, and source code are available at https://github.com/SYSUSELab/MultiCodeIF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Over more than two decades, The University of Glasgow has co-designed and delivered numerous software engineering focused courses with industry partners, covering both technical and discipline specific professional skills. Such collaborations are not unique and many of the benefits are well recognised in the literature. These include enhancing the real-world relevance of curricula, developing student professional networks ahead of graduation and easing recruitment opportunities for employers. However, there is relatively little scholarship on the perspectives of industry practitioners who participate in course design and delivery. This gap is significant, since the effort invested by practitioners is often substantial and may require ongoing support from both the industry partner and academic institution. Understanding the motivations, expectations and experiences of practitioners who engage in course delivery can guide the formation of future partnerships and ensure their long-term sustainability. We begin to address this gap by reporting on the outcomes of a retrospective conducted amongst the practitioner coauthors of this paper, with the academic coauthors acting as facilitators. All coauthors have participated in the recent co-design and delivery of software engineering courses, but we choose to focus explicitly on the perspectives of the practitioners. We report on the themes that emerged from the discussions and our resulting recommendations for future collaborations. </t>
+  </si>
+  <si>
+    <t>Software Engineering for Large Language Models: Research Status, Challenges and the Road Ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The rapid advancement of large language models (LLMs) has redefined artificial intelligence (AI), pushing the boundaries of AI research and enabling unbounded possibilities for both academia and the industry. However, LLM development faces increasingly complex challenges throughout its lifecycle, yet no existing research systematically explores these challenges and solutions from the perspective of software engineering (SE) approaches. To fill the gap, we systematically analyze research status throughout the LLM development lifecycle, divided into six phases: requirements engineering, dataset construction, model development and enhancement, testing and evaluation, deployment and operations, and maintenance and evolution. We then conclude by identifying the key challenges for each phase and presenting potential research directions to address these challenges. In general, we provide valuable insights from an SE perspective to facilitate future advances in LLM development. </t>
+  </si>
+  <si>
+    <t>How (Not) To Write a Software Engineering Abstract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background: Abstracts are a particularly valuable element in a software engineering research article. However, not all abstracts are as informative as they could be. Objective: Characterize the structure of abstracts in high-quality software engineering venues. Observe and quantify deficiencies. Suggest guidelines for writing informative abstracts. Methods: Use qualitative open coding to derive concepts that explain relevant properties of abstracts. Identify the archetypical structure of abstracts. Use quantitative content analysis to objectively characterize abstract structure of a sample of 362 abstracts from five presumably high-quality venues. Use exploratory data analysis to find recurring issues in abstracts. Compare the archetypical structure to actual structures. Infer guidelines for producing informative abstracts. Results: Only 29% of the sampled abstracts are complete, i.e., provide background, objective, method, result, and conclusion information. For structured abstracts, the ratio is twice as big. Only 4% of the abstracts are proper, i.e., they also have good readability (Flesch-Kincaid score) and have no informativeness gaps, understandability gaps, nor highly ambiguous sentences. Conclusions: (1) Even in top venues, a large majority of abstracts are far from ideal. (2) Structured abstracts tend to be better than unstructured ones. (3) Artifact-centric works need a different structured format. (4) The community should start requiring conclusions that generalize, which currently are often missing in abstracts. </t>
+  </si>
+  <si>
+    <t>Ten simple rules for PIs to integrate Research Software Engineering into their research group</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Research Software Engineering (RSEng) is a key success factor in producing high-quality research software, which in turn enables and improves research outcomes. However, as a principal investigator or leader of a research group you may not know what RSEng is, where to get started with it, or how to use it to maximize its benefit for your research. RSEng also often comes with technical complexity, and therefore reduced accessibility to some researchers. The ten simple rules presented in this paper aim to improve the accessibility of RSEng, and provide practical and actionable advice to PIs and leaders for integrating RSEng into their research group. By following these rules, readers can improve the quality, reproducibility, and trustworthiness of their research software, ultimately leading to better, more reproducible and more trustworthy research outcomes. </t>
+  </si>
+  <si>
+    <t>Skywork-SWE: Unveiling Data Scaling Laws for Software Engineering in LLMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software engineering (SWE) has recently emerged as a crucial testbed for next-generation LLM agents, demanding inherent capabilities in two critical dimensions: sustained iterative problem-solving (e.g., &gt;50 interaction rounds) and long-context dependency resolution (e.g., &gt;32k tokens). However, the data curation process in SWE remains notoriously time-consuming, as it heavily relies on manual annotation for code file filtering and the setup of dedicated runtime environments to execute and validate unit tests. Consequently, most existing datasets are limited to only a few thousand GitHub-sourced instances. To this end, we propose an incremental, automated data-curation pipeline that systematically scales both the volume and diversity of SWE datasets. Our dataset comprises 10,169 real-world Python task instances from 2,531 distinct GitHub repositories, each accompanied by a task specified in natural language and a dedicated runtime-environment image for automated unit-test validation. We have carefully curated over 8,000 successfully runtime-validated training trajectories from our proposed SWE dataset. When fine-tuning the Skywork-SWE model on these trajectories, we uncover a striking data scaling phenomenon: the trained model's performance for software engineering capabilities in LLMs continues to improve as the data size increases, showing no signs of saturation. Notably, our Skywork-SWE model achieves 38.0% pass@1 accuracy on the SWE-bench Verified benchmark without using verifiers or multiple rollouts, establishing a new state-of-the-art (SOTA) among the Qwen2.5-Coder-32B-based LLMs built on the OpenHands agent framework. Furthermore, with the incorporation of test-time scaling techniques, the performance further improves to 47.0% accuracy, surpassing the previous SOTA results for sub-32B parameter models. We release the Skywork-SWE-32B model checkpoint to accelerate future research. </t>
+  </si>
+  <si>
+    <t>Understanding Software Engineering Agents: A Study of Thought-Action-Result Trajectories</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Model (LLM)-based agents are increasingly employed to automate complex software engineering tasks such as program repair and issue resolution. These agents operate by autonomously generating natural language thoughts, invoking external tools, and iteratively refining their solutions. Despite their widespread adoption, the internal decision-making processes of these agents remain largely unexplored, limiting our understanding of their operational dynamics and failure modes. In this paper, we present a large-scale empirical study of the thought-action-result trajectories of three state-of-the-art LLM-based agents: \textsc{RepairAgent}, \textsc{AutoCodeRover}, and \textsc{OpenHands}. We unify their interaction logs into a common format, capturing 120 trajectories and 2822 LLM interactions focused on program repair and issue resolution. Our study combines quantitative analyses of structural properties, action patterns, and token usage with qualitative assessments of reasoning coherence and feedback integration. We identify key trajectory characteristics such as iteration counts and token consumption, recurring action sequences, and the semantic coherence linking thoughts, actions, and their results. Our findings reveal behavioral motifs and anti-patterns that distinguish successful from failed executions, providing actionable insights for improving agent design, including prompting strategies, failure diagnosis, and anti-pattern detection. We release our dataset and annotation framework to support further research on transparent and robust autonomous software engineering agents.</t>
+  </si>
+  <si>
+    <t>Software Reuse in the Generative AI Era: From Cargo Cult Towards AI Native Software Engineering</t>
+  </si>
+  <si>
+    <t>Software development is currently under a paradigm shift in which artificial intelligence and generative software reuse are taking the center stage in software creation. Consequently, earlier software reuse practices and methods are rapidly being replaced by AI-assisted approaches in which developers place their trust on code that has been generated by artificial intelligence. This is leading to a new form of software reuse that is conceptually not all that different from cargo cult development. In this paper we discuss the implications of AI-assisted generative software reuse in the context of emerging "AI native" software engineering, bring forth relevant questions, and define a tentative research agenda and call to action for tackling some of the central issues associated with this approach.</t>
+  </si>
+  <si>
+    <t>Is Your Automated Software Engineer Trustworthy?</t>
+  </si>
+  <si>
+    <t>Large Language Models (LLMs) are being increasingly used in software engineering tasks, with an increased focus on bug report resolution over the past year. However, most proposed systems fail to properly handle uncertain or incorrect inputs and outputs. Existing LLM-based tools and coding agents respond to every issue and generate a patch for every case, even when the input is vague or their own output is incorrect. There are no mechanisms in place to abstain when confidence is low. This leads to unreliable behaviour, such as hallucinated code changes or responses based on vague issue reports. We introduce BouncerBench, a benchmark that evaluates whether LLM-based software agents can refuse to act when inputs are ill-defined or refuse to respond when their own outputs are likely to be incorrect. Unlike prior benchmarks that implicitly incentivize models to generate responses even when uncertain, BouncerBench aims to improve precision by targeting two overlooked failure points: (1) vague or underspecified issue descriptions in tickets and (2) logically or functionally incorrect code patches created by the system. It measures whether proposed systems can distinguish actionable issues from vague tickets and valid patches from untrustworthy ones. We also implement a basic input and output bouncer, evaluating how well current LLMs can abstain when needed. Our results show that most models fail to abstain from underspecified inputs or incorrect outputs. Hence, we conclude that there is significant room for improvement before LLMs can be trusted to make correct decisions and recommendations in real-world software engineering workflows. BouncerBench provides a first step toward evaluating and building more cautious, trustworthy code agents. The replication package, dataset, and leaderboard can be found at bouncerbench.com</t>
+  </si>
+  <si>
+    <t>PAGENT: Learning to Patch Software Engineering Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM Agents produce patches automatically to resolve an issue. However, they can generate inaccurate patches. Little is known about the root causes behind those failed patches or how those could be fixed. This paper reports an empirical study of the failed patches generated by seven top LLM code agents. We collected 114 issues from the SWE-bench Lite dataset that remained unresolved across the agents. The seven agents produced a total of 769 failed patches for those issues, which we checked with a combination of GPT-4o and manual analysis. We present a taxonomy of the failure reasons across the patches. The taxonomy contains six categories, with several sub-categories under each category. For example, a frequently observed category is the inability of an LLM to correctly infer/produce the appropriate variable type in the produced patch. As a first step towards addressing such type-related errors, we designed PAGENT (Patch Agent). PAGENT utilizes program analysis techniques like CFG creation and exploration to infer the type of information of a patch. PAGENT does this by applying repository-level static code analysis techniques. Then, PAGENT refines the inferred type by further utilizing an LLM-based inference technique. We tested PAGENT on all 127 type-related failed patches from the top three agents in our study. PAGENT could fix 29 of the 127 failed patches. </t>
+  </si>
+  <si>
+    <t>Quantum Optimization for Software Engineering: A Survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quantum computing, particularly in the area of quantum optimization, is steadily progressing toward practical applications, supported by an expanding range of hardware platforms and simulators. While Software Engineering (SE) optimization has a strong foundation, which is exemplified by the active Search-Based Software Engineering (SBSE) community and numerous classical optimization methods, the growing complexity of modern software systems and their engineering processes demands innovative solutions. This Systematic Literature Review (SLR) focuses specifically on studying the literature that applies quantum or quantum-inspired algorithms to solve classical SE optimization problems. We examine 77 primary studies selected from an initial pool of 2083 publications obtained through systematic searches of six digital databases using carefully crafted search strings. Our findings reveal concentrated research efforts in areas such as SE operations and software testing, while exposing significant gaps across other SE activities. Additionally, the SLR uncovers relevant works published outside traditional SE venues, underscoring the necessity of this comprehensive review. Overall, our study provides a broad overview of the research landscape, empowering the SBSE community to leverage quantum advancements in addressing next-generation SE challenges.</t>
+  </si>
+  <si>
+    <t>LLMs in Coding and their Impact on the Commercial Software Engineering Landscape</t>
+  </si>
+  <si>
+    <t>Large-language-model coding tools are now mainstream in software engineering. But as these same tools move human effort up the development stack, they present fresh dangers: 10% of real prompts leak private data, 42% of generated snippets hide security flaws, and the models can even ``agree'' with wrong ideas, a trait called sycophancy. We argue that firms must tag and review every AI-generated line of code, keep prompts and outputs inside private or on-premises deployments, obey emerging safety regulations, and add tests that catch sycophantic answers -- so they can gain speed without losing security and accuracy.</t>
+  </si>
+  <si>
+    <t>The growth of Large Language Model (LLM) technology has raised expectations for automated coding. However, software engineering is more than coding and is concerned with activities including maintenance and evolution of a project. In this context, the concept of LLM agents has gained traction, which utilize LLMs as reasoning engines to invoke external tools autonomously. But is an LLM agent the same as an AI software engineer? In this paper, we seek to understand this question by developing a Unified Software Engineering agent or USEagent. Unlike existing work which builds specialized agents for specific software tasks such as testing, debugging, and repair, our goal is to build a unified agent which can orchestrate and handle multiple capabilities. This gives the agent the promise of handling complex scenarios in software development such as fixing an incomplete patch, adding new features, or taking over code written by others. We envision USEagent as the first draft of a future AI Software Engineer which can be a team member in future software development teams involving both AI and humans. To evaluate the efficacy of USEagent, we build a Unified Software Engineering bench (USEbench) comprising of myriad tasks such as coding, testing, and patching. USEbench is a judicious mixture of tasks from existing benchmarks such as SWE-bench, SWT-bench, and REPOCOD. In an evaluation on USEbench consisting of 1,271 repository-level software engineering tasks, USEagent shows improved efficacy compared to existing general agents such as OpenHands CodeActAgent. There exist gaps in the capabilities of USEagent for certain coding tasks, which provides hints on further developing the AI Software Engineer of the future</t>
+  </si>
+  <si>
+    <t>The Tech DEI Backlash -- The Changing Landscape of Diversity, Equity, and Inclusion in Software Engineering</t>
+  </si>
+  <si>
+    <t>Not long ago, Diversity, Equity, and Inclusion (DEI) initiatives were a top priority for leading software companies. However, in a short period, a wave of backlash has led many firms to re-assess their DEI strategies. Responding to this DEI backlash is crucial in academic research, especially because, currently, little scholarly research has been done on it. In this paper, therefore, we have set forth the following research question (RQ): "How have leading software companies changed their DEI strategies in recent years?" Given the novelty of the RQ and, consequently, the lack of scholarly research on it, we are conducting a grey literature study, examining the current state of DEI initiatives in 10 leading software companies. Based on our analysis, we have classified companies into categories based on their shift in commitment to DEI. We can identify that companies are indeed responding to the backlash by rethinking their strategy, either by reducing, increasing, or renaming their DEI initiatives. In contrast, some companies keep on with their DEI strategy, at least so far, despite the challenging political climate. To illustrate these changes, we introduce the DEI Universe Map, a visual representation of software industry trends in DEI commitment and actions.</t>
+  </si>
+  <si>
+    <t>Get on the Train or be Left on the Station: Using LLMs for Software Engineering Research</t>
+  </si>
+  <si>
+    <t>The adoption of Large Language Models (LLMs) is not only transforming software engineering (SE) practice but is also poised to fundamentally disrupt how research is conducted in the field. While perspectives on this transformation range from viewing LLMs as mere productivity tools to considering them revolutionary forces, we argue that the SE research community must proactively engage with and shape the integration of LLMs into research practices, emphasizing human agency in this transformation. As LLMs rapidly become integral to SE research - both as tools that support investigations and as subjects of study - a human-centric perspective is essential. Ensuring human oversight and interpretability is necessary for upholding scientific rigor, fostering ethical responsibility, and driving advancements in the field. Drawing from discussions at the 2nd Copenhagen Symposium on Human-Centered AI in SE, this position paper employs McLuhan's Tetrad of Media Laws to analyze the impact of LLMs on SE research. Through this theoretical lens, we examine how LLMs enhance research capabilities through accelerated ideation and automated processes, make some traditional research practices obsolete, retrieve valuable aspects of historical research approaches, and risk reversal effects when taken to extremes. Our analysis reveals opportunities for innovation and potential pitfalls that require careful consideration. We conclude with a call to action for the SE research community to proactively harness the benefits of LLMs while developing frameworks and guidelines to mitigate their risks, to ensure continued rigor and impact of research in an AI-augmented futur</t>
+  </si>
+  <si>
+    <t>A Mapping Study About Training in Industry Context in Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context: Corporate training plays a strategic role in the continuous development of professionals in the software engineering industry. However, there is a lack of systematized understanding of how training initiatives are designed, implemented, and evaluated within this domain. Objective: This study aims to map the current state of research on corporate training in software engineering in industry settings, using Eduardo Salas' training framework as an analytical lens. Method: A systematic mapping study was conducted involving the selection and analysis of 26 primary studies published in the field. Each study was categorized according to Salas' four key areas: Training Needs Analysis, Antecedent Training Conditions, Training Methods and Instructional Strategies, and Post-Training Conditions. Results: The findings show a predominance of studies focusing on Training Methods and Instructional Strategies. Significant gaps were identified in other areas, particularly regarding Job/Task Analysis and Simulation-based Training and Games. Most studies were experience reports, lacking methodological rigor and longitudinal assessment. Conclusions: The study offers a structured overview of how corporate training is approached in software engineering, revealing underexplored areas and proposing directions for future research. It contributes to both academic and practical communities by highlighting challenges, methodological trends, and opportunities for designing more effective training programs in industry. </t>
+  </si>
+  <si>
+    <t>Sharp Tools: How Developers Wield Agentic AI in Real Software Engineering Tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software Engineering Agents (SWE agents) can autonomously perform development tasks on benchmarks like SWE Bench, but still face challenges when tackling complex and ambiguous real-world tasks. Consequently, SWE agents are often designed to allow interactivity with developers, enabling collaborative problem-solving. To understand how developers collaborate with SWE agents and the communication challenges that arise in such interactions, we observed 19 developers using an in-IDE agent to resolve 33 open issues in repositories to which they had previously contributed. Participants successfully resolved about half of these issues, with participants solving issues incrementally having greater success than those using a one-shot approach. Participants who actively collaborated with the agent and iterated on its outputs were also more successful, though they faced challenges in trusting the agent's responses and collaborating on debugging and testing. These results have implications for successful developer-agent collaborations, and for the design of more effective SWE agents.</t>
+  </si>
+  <si>
+    <t>An Empirical study on LLM-based Log Retrieval for Software Engineering Metadata Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Developing autonomous driving systems (ADSs) involves generating and storing extensive log data from test drives, which is essential for verification, research, and simulation. However, these high-frequency logs, recorded over varying durations, pose challenges for developers attempting to locate specific driving scenarios. This difficulty arises due to the wide range of signals representing various vehicle components and driving conditions, as well as unfamiliarity of some developers' with the detailed meaning of these signals. Traditional SQL-based querying exacerbates this challenge by demanding both domain expertise and database knowledge, often yielding results that are difficult to verify for accuracy. This paper introduces a Large Language Model (LLM)-supported approach that combines signal log data with video recordings from test drives, enabling natural language based scenario searches while reducing the need for specialized knowledge. By leveraging scenario distance graphs and relative gap indicators, it provides quantifiable metrics to evaluate the reliability of query results. The method is implemented as an API for efficient database querying and retrieval of relevant records, paired with video frames for intuitive visualization. Evaluation on an open industrial dataset demonstrates improved efficiency and reliability in scenario retrieval, eliminating dependency on a single data source and conventional SQL.</t>
+  </si>
+  <si>
+    <t>Augmenting the Generality and Performance of Large Language Models for Software Engineering</t>
+  </si>
+  <si>
+    <t>Large Language Models (LLMs) are revolutionizing software engineering (SE), with special emphasis on code generation and analysis. However, their applications to broader SE practices including conceptualization, design, and other non-code tasks, remain partially underexplored. This research aims to augment the generality and performance of LLMs for SE by (1) advancing the understanding of how LLMs with different characteristics perform on various non-code tasks, (2) evaluating them as sources of foundational knowledge in SE, and (3) effectively detecting hallucinations on SE statements. The expected contributions include a variety of LLMs trained and evaluated on domain-specific datasets, new benchmarks on foundational knowledge in SE, and methods for detecting hallucinations. Initial results in terms of performance improvements on various non-code tasks are promising.</t>
+  </si>
+  <si>
+    <t>Agent-RLVR: Training Software Engineering Agents via Guidance and Environment Rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinforcement Learning from Verifiable Rewards (RLVR) has been widely adopted as the de facto method for enhancing the reasoning capabilities of large language models and has demonstrated notable success in verifiable domains like math and competitive programming tasks. However, the efficacy of RLVR diminishes significantly when applied to agentic environments. These settings, characterized by multi-step, complex problem solving, lead to high failure rates even for frontier LLMs, as the reward landscape is too sparse for effective model training via conventional RLVR. In this work, we introduce Agent-RLVR, a framework that makes RLVR effective in challenging agentic settings, with an initial focus on software engineering tasks. Inspired by human pedagogy, Agent-RLVR introduces agent guidance, a mechanism that actively steers the agent towards successful trajectories by leveraging diverse informational cues. These cues, ranging from high-level strategic plans to dynamic feedback on the agent's errors and environmental interactions, emulate a teacher's guidance, enabling the agent to navigate difficult solution spaces and promotes active self-improvement via additional environment exploration. In the Agent-RLVR training loop, agents first attempt to solve tasks to produce initial trajectories, which are then validated by unit tests and supplemented with agent guidance. Agents then reattempt with guidance, and the agent policy is updated with RLVR based on the rewards of these guided trajectories. Agent-RLVR elevates the pass@1 performance of Qwen-2.5-72B-Instruct from 9.4% to 22.4% on SWE-Bench Verified. We find that our guidance-augmented RLVR data is additionally useful for test-time reward model training, shown by further boosting pass@1 to 27.8%. Agent-RLVR lays the groundwork for training agents with RLVR in complex, real-world environments where conventional RL methods struggle. </t>
+  </si>
+  <si>
+    <t>Toward a Brazilian Research Agenda in Quantum Software Engineering: A Systematic Mapping Study</t>
+  </si>
+  <si>
+    <t>Context: Quantum Software Engineering (QSE) has emerged as a promising discipline to support the development of quantum applications by integrating quantum computing principles with established software engineering practices. Problem: Despite recent growth, QSE still lacks standardized methodologies, tools, and guidelines. Moreover, countries like Brazil have had minimal representation in the development of this emerging field. Objective: This study aims to map the current state of QSE by identifying research trends, contributions, and gaps that can inform future investigations and strategic initiatives. Methodology: A systematic mapping study was conducted across major scientific databases, retrieving 3,219 studies. After applying inclusion and exclusion criteria, 3,052 studies were excluded, resulting in 167 selected for analysis. The publications were classified by study type, research type, and alignment with SWEBOK knowledge areas. Results: Most studies focused on Software Engineering Models and Methods, Software Architecture, and Software Testing. Conceptual and technical proposals were predominant, while empirical validations remained limited. Conclusions: QSE is still a maturing field. Advancing it requires standardization, more empirical research, and greater participation from developing countries. As its main contribution, this study proposes a Brazilian Research Agenda in QSE to guide national efforts and foster the development of a strong local scientific community.</t>
+  </si>
+  <si>
+    <t>Notes On Writing Effective Empirical Software Engineering Papers: An Opinionated Primer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> While mastered by some, good scientific writing practices within Empirical Software Engineering (ESE) research appear to be seldom discussed and documented. Despite this, these practices are implicit or even explicit evaluation criteria of typical software engineering conferences and journals. In this pragmatic, educational-first document, we want to provide guidance to those who may feel overwhelmed or confused by writing ESE papers, but also those more experienced who still might find an opinionated collection of writing advice useful. The primary audience we had in mind for this paper were our own BSc, MSc, and PhD students, but also students of others. Our documented advice therefore reflects a subjective and personal vision of writing ESE papers. By no means do we claim to be fully objective, generalizable, or representative of the whole discipline. With that being said, writing papers in this way has worked pretty well for us so far. We hope that this guide can at least partially do the same for others. </t>
+  </si>
+  <si>
+    <t>Chain of Draft for Software Engineering: Challenges in Applying Concise Reasoning to Code Tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large language models (LLMs) have become vital tools for software development, but they often require verbose intermediate reasoning for complex code tasks, leading to high latency and costs. This research extends the Chain of Draft (CoD) method to software engineering, designing and evaluating multiple CoD variants tailored for code tasks. Through comprehensive experiments on all 300 samples from the SWE-bench benchmark, we found that all CoD variants used significantly fewer tokens than Chain of Thought (CoT), with Baseline CoD being most efficient at 55.4% of CoT's tokens. While this represents substantial efficiency gains - translating to approximately 45% reduction in processing time and API costs - it differs from the extreme 7.6% reported in the original CoD paper for mathematical reasoning. This difference stems from the inherent complexity and context-dependency of software tasks, which require more detailed reasoning to maintain solution quality. Our multi-dimensional quality assessment revealed that CoD variants maintain over 90% of CoT's code quality across key metrics including correctness, compatibility, and maintainability, making them practical alternatives for real-world development scenarios where efficiency matters. This research demonstrates how domain-specific characteristics influence prompting strategy effectiveness and provides a framework for balancing efficiency with solution quality in software engineering applications. Our findings offer practical guidance for optimizing LLM-based development workflows through appropriate prompting strategy selection based on project requirements</t>
+  </si>
+  <si>
+    <t>Evaluating Large Language Models on Non-Code Software Engineering Tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Models (LLMs) have demonstrated remarkable capabilities in code understanding and generation; however, their effectiveness on non-code Software Engineering (SE) tasks remains underexplored. We present the first comprehensive benchmark, which we name `Software Engineering Language Understanding' (SELU), for evaluating LLMs on 17 non-code tasks, spanning from identifying whether a requirement is functional or non-functional to estimating the effort and complexity of backlog items. SELU covers classification, regression, Named Entity Recognition (NER), and Masked Language Modeling (MLM) targets, with data drawn from diverse sources such as code repositories, issue tracking systems, and developer forums. We fine-tune 22 open-source LLMs, prompt two proprietary alternatives, and train two baselines. Performance is measured using metrics such as F1-macro, SMAPE, F1-micro, and accuracy, and compared via the Bayesian signed-rank test. Our results show that moderate-scale decoder-only models consistently form a top-tier, exhibiting high mean performance and low across-task variance, while domain adaptation via code-focused pre-training might yield only modest improvements. These insights guide model selection for non-code SE workflows and highlight directions for expanding SELU to generative and design-oriented scenarios.</t>
+  </si>
+  <si>
+    <t>SWE-Flow: Synthesizing Software Engineering Data in a Test-Driven Manner</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> We introduce **SWE-Flow**, a novel data synthesis framework grounded in Test-Driven Development (TDD). Unlike existing software engineering data that rely on human-submitted issues, **SWE-Flow** automatically infers incremental development steps directly from unit tests, which inherently encapsulate high-level requirements. The core of **SWE-Flow** is the construction of a Runtime Dependency Graph (RDG), which precisely captures function interactions, enabling the generation of a structured, step-by-step *development schedule*. At each step, **SWE-Flow** produces a partial codebase, the corresponding unit tests, and the necessary code modifications, resulting in fully verifiable TDD tasks. With this approach, we generated 16,061 training instances and 2,020 test instances from real-world GitHub projects, creating the **SWE-Flow-Eval** benchmark. Our experiments show that fine-tuning open model on this dataset significantly improves performance in TDD-based coding. To facilitate further research, we release all code, datasets, models, and Docker images at [Github](https://github.com/Hambaobao/SWE-Flow). </t>
+  </si>
+  <si>
+    <t>Understanding Software Engineering Agents Through the Lens of Traceability: An Empirical Study</t>
+  </si>
+  <si>
+    <t>With the advent of large language models (LLMs), software engineering agents (SWE agents) have emerged as a powerful paradigm for automating a range of software tasks -- from code generation and repair to test case synthesis. These agents operate autonomously by interpreting user input and responding to environmental feedback. While various agent architectures have demonstrated strong empirical performance, the internal decision-making worfklows that drive their behavior remain poorly understood. Deeper insight into these workflows hold promise for improving both agent reliability and efficiency. In this work, we present the first systematic study of SWE agent behavior through the lens of execution traces. Our contributions are as follows: (1) we propose the first taxonomy of decision-making pathways across five representative agents; (2) using this taxonomy, we identify three core components essential to agent success -- bug localization, patch generation, and reproduction test generation -- and study each in depth; (3) we study the impact of test generation on successful patch production; and analyze strategies that can lead to successful test generation; (4) we further conduct the first large-scale code clone analysis comparing agent-generated and developer-written patches and provide a qualitative study revealing structural and stylistic differences in patch content. Together, these findings offer novel insights into agent design and open avenues for building agents that are both more effective and more aligned with human development practices.</t>
+  </si>
+  <si>
+    <t>MBTModelGenerator: A software tool for reverse engineering of Model-based Testing (MBT) models from clickstream data of web applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated testing has become a standard practice in software engineering, yet the creation of test models and suites remains labor-intensive. To reduce this effort, we developed an open-source tool that automatically generates Model-Based Testing (MBT) models from clickstream data collected during user interaction with web applications. The tool captures UI events, transforms them into state-transition models, and exports the result in a format compatible with the GraphWalker MBT tool. This enables immediate test execution without the need for manual model creation. The approach lowers the barrier to MBT adoption by leveraging actual usage behavior and reducing the reliance on upfront modeling. This technical report documents the system requirements, design decisions, implementation details, testing process, and empirical evaluation of the tool, which is publicly available as open-source. </t>
+  </si>
+  <si>
+    <t>SWE-Dev: Building Software Engineering Agents with Training and Inference Scaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large language models (LLMs) have advanced rapidly from conversational problem solving to addressing real-world tasks involving tool use, such as software engineering (SWE). Recent LLM-powered toolkits, such as OpenAI Codex and Cursor, have offered end-to-end automation of the software development process. However, building effective SWE agents remains challenging due to the lack of high-quality training data and effective test cases. To address this issue, we present SWE-Dev, an SWE agent built upon open-source LLMs. First, we develop a robust pipeline to synthesize test cases for patch evaluation. Second, we scale up agent trajectories to construct the training data for building SWE-Dev. Experiments on the SWE-bench-Verified benchmark show that the SWE-Dev models can achieve top performance among all open SWE agents. Specifically, the success rates of the SWE-Dev 7B and 32B parameter models reach 23.4% and 36.6%, respectively, outperforming state-of-the-art open-source models. All code, models, and datasets are publicly available at https://github.com/THUDM/SWE-Dev.</t>
+  </si>
+  <si>
+    <r>
+      <t>Which Prompting Technique Should I Use? An Empirical Investigation of Prompting Techniques for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF287916"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Software</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF287916"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Tasks</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A growing variety of prompt engineering techniques has been proposed for Large Language Models (LLMs), yet systematic evaluation of each technique on individual software engineering (SE) tasks remains underexplored. In this study, we present a systematic evaluation of 14 established prompt techniques across 10 SE tasks using four LLM models. As identified in the prior literature, the selected prompting techniques span six core dimensions (Zero-Shot, Few-Shot, Thought Generation, Ensembling, Self-Criticism, and Decomposition). They are evaluated on tasks such as code generation, bug fixing, and code-oriented question answering, to name a few. Our results show which prompting techniques are most effective for SE tasks requiring complex logic and intensive reasoning versus those that rely more on contextual understanding and example-driven scenarios. We also analyze correlations between the linguistic characteristics of prompts and the factors that contribute to the effectiveness of prompting techniques in enhancing performance on SE tasks. Additionally, we report the time and token consumption for each prompting technique when applied to a specific task and model, offering guidance for practitioners in selecting the optimal prompting technique for their use cases. </t>
+  </si>
+  <si>
+    <t>Differences between Neurodivergent and Neurotypical Software Engineers: Analyzing the 2022 Stack Overflow Survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurodiversity describes variation in brain function among people, including common conditions such as Autism spectrum disorder (ASD), Attention deficit hyperactivity disorder (ADHD), and dyslexia. While Software Engineering (SE) literature has started to explore the experiences of neurodivergent software engineers, there is a lack of research that compares their challenges to those of neurotypical software engineers. To address this gap, we analyze existing data from the 2022 Stack Overflow Developer survey that collected data on neurodiversity. We quantitatively compare the answers of professional engineers with ASD (n=374), ADHD (n=1305), and dyslexia (n=363) with neurotypical engineers. Our findings indicate that neurodivergent engineers face more difficulties than neurotypical engineers. Specifically, engineers with ADHD report that they face more interruptions caused by waiting for answers, and that they less frequently interact with individuals outside their team. This study provides a baseline for future research comparing neurodivergent engineers with neurotypical ones. Several factors in the Stack Overflow survey and in our analysis are likely to lead to conservative estimates of the actual effects between neurodivergent and neurotypical engineers, e.g., the effects of the COVID-19 pandemic and our focus on employed professionals. </t>
+  </si>
+  <si>
+    <t>Beyond C/C++: Probabilistic and LLM Methods for Next-Generation Software Reverse Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This proposal discusses the growing challenges in reverse engineering modern software binaries, particularly those compiled from newer system programming languages such as Rust, Go, and Mojo. Traditional reverse engineering techniques, developed with a focus on C and C++, fall short when applied to these newer languages due to their reliance on outdated heuristics and failure to fully utilize the rich semantic information embedded in binary programs. These challenges are exacerbated by the limitations of current data-driven methods, which are susceptible to generating inaccurate results, commonly referred to as hallucinations. To overcome these limitations, we propose a novel approach that integrates probabilistic binary analysis with fine-tuned large language models (LLMs). Our method systematically models the uncertainties inherent in reverse engineering, enabling more accurate reasoning about incomplete or ambiguous information. By incorporating LLMs, we extend the analysis beyond traditional heuristics, allowing for more creative and context-aware inferences, particularly for binaries from diverse programming languages. This hybrid approach not only enhances the robustness and accuracy of reverse engineering efforts but also offers a scalable solution adaptable to the rapidly evolving landscape of software development</t>
+  </si>
+  <si>
+    <t>How do Pre-Trained Models Support Software Engineering? An Empirical Study in Hugging Face</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Open-Source Pre-Trained Models (PTMs) provide extensive resources for various Machine Learning (ML) tasks, yet these resources lack a classification tailored to Software Engineering (SE) needs. To address this gap, we derive a taxonomy encompassing 147 SE tasks and apply an SE-oriented classification to PTMs in a popular open-source ML repository, Hugging Face (HF). Our repository mining study began with a systematically gathered database of PTMs from the HF API, considering their model card descriptions and metadata, and the abstract of the associated arXiv papers. We confirmed SE relevance through multiple filtering steps: detecting outliers, identifying near-identical PTMs, and the use of Gemini 2.0 Flash, which was validated with five pilot studies involving three human annotators. This approach uncovered 2,205 SE PTMs. We find that code generation is the most common SE task among PTMs, primarily focusing on software implementation, while requirements engineering and software design activities receive limited attention. In terms of ML tasks, text generation dominates within SE PTMs. Notably, the number of SE PTMs has increased markedly since 2023 Q2. Our classification provides a solid foundation for future automated SE scenarios, such as the sampling and selection of suitable PTMs.</t>
+  </si>
+  <si>
+    <t>Ten Simple Rules for Catalyzing Collaborations and Building Bridges between Research Software Engineers and Software Engineering Researchers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In the evolving landscape of scientific and scholarly research, effective collaboration between Research Software Engineers (RSEs) and Software Engineering Researchers (SERs) is pivotal for advancing innovation and ensuring the integrity of computational methodologies. This paper presents ten strategic guidelines aimed at fostering productive partnerships between these two distinct yet complementary communities. The guidelines emphasize the importance of recognizing and respecting the cultural and operational differences between RSEs and SERs, proactively initiating and nurturing collaborations, and engaging within each other's professional environments. They advocate for identifying shared challenges, maintaining openness to emerging problems, ensuring mutual benefits, and serving as advocates for one another. Additionally, the guidelines highlight the necessity of vigilance in monitoring collaboration dynamics, securing institutional support, and defining clear, shared objectives. By adhering to these principles, RSEs and SERs can build synergistic relationships that enhance the quality and impact of research outcomes</t>
+  </si>
+  <si>
+    <t>Encouraging Students' Responsible Use of GenAI in Software Engineering Education: A Causal Model and Two Institutional Applications</t>
+  </si>
+  <si>
+    <t>Context: As generative AI (GenAI) tools such as ChatGPT and GitHub Copilot become pervasive in education, concerns are rising about students using them to complete rather than learn from coursework-risking overreliance, reduced critical thinking, and long-term skill deficits. Objective: This paper proposes and empirically applies a causal model to help educators scaffold responsible GenAI use in Software Engineering (SE) education. The model identifies how professor actions, student factors, and GenAI tool characteristics influence students' usage of GenAI tools. Method: Using a design-based research approach, we applied the model in two contexts: (1) revising four extensive lab assignments of a final-year Software Testing course at Queen's University Belfast (QUB), and (2) embedding GenAI-related competencies into the curriculum of a newly developed SE BSc program at Azerbaijan Technical University (AzTU). Interventions included GenAI usage declarations, output validation tasks, peer-review of AI artifacts, and career-relevant messaging. Results: In the course-level case, instructor observations and student artifacts indicated increased critical engagement with GenAI, reduced passive reliance, and improved awareness of validation practices. In the curriculum-level case, the model guided integration of GenAI learning outcomes across multiple modules and levels, enabling longitudinal scaffolding of AI literacy. Conclusion: The causal model served as both a design scaffold and a reflection tool. It helped align GenAI-related pedagogy with SE education goals and can offer a useful framework for instructors and curriculum designers navigating the challenges of GenAI-era education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum-Based Software Engineering
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quantum computing has demonstrated the potential to solve computationally intensive problems more efficiently than classical methods. Many software engineering tasks, such as test case selection, static analysis, code clone detection, and defect prediction, involve complex optimization, search, or classification, making them candidates for quantum enhancement. In this paper, we introduce Quantum-Based Software Engineering (QBSE) as a new research direction for applying quantum computing to classical software engineering problems. We outline its scope, clarify its distinction from quantum software engineering (QSE), and identify key problem types that may benefit from quantum optimization, search, and learning techniques. We also summarize existing research efforts that remain fragmented. Finally, we outline a preliminary research agenda that may help guide the future development of QBSE, providing a structured and meaningful direction within software engineering.</t>
+  </si>
+  <si>
+    <t>Satori-SWE: Evolutionary Test-Time Scaling for Sample-Efficient Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language models (LMs) perform well on standardized coding benchmarks but struggle with real-world software engineering tasks such as resolving GitHub issues in SWE-Bench, especially when model parameters are less than 100B. While smaller models are preferable in practice due to their lower computational cost, improving their performance remains challenging. Existing approaches primarily rely on supervised fine-tuning (SFT) with high-quality data, which is expensive to curate at scale. An alternative is test-time scaling: generating multiple outputs, scoring them using a verifier, and selecting the best one. Although effective, this strategy often requires excessive sampling and costly scoring, limiting its practical application. We propose Evolutionary Test-Time Scaling (EvoScale), a sample-efficient method that treats generation as an evolutionary process. By iteratively refining outputs via selection and mutation, EvoScale shifts the output distribution toward higher-scoring regions, reducing the number of samples needed to find correct solutions. To reduce the overhead from repeatedly sampling and selection, we train the model to self-evolve using reinforcement learning (RL). Rather than relying on external verifiers at inference time, the model learns to self-improve the scores of its own generations across iterations. Evaluated on SWE-Bench-Verified, EvoScale enables our 32B model, Satori-SWE-32B, to match or exceed the performance of models with over 100B parameters while using a few samples. Code, data, and models will be fully open-sourced. </t>
+  </si>
+  <si>
+    <t>From Knowledge to Noise: CTIM-Rover and the Pitfalls of Episodic Memory in Software Engineering Agents</t>
+  </si>
+  <si>
+    <t>We introduce CTIM-Rover, an AI agent for Software Engineering (SE) built on top of AutoCodeRover (Zhang et al., 2024) that extends agentic reasoning frameworks with an episodic memory, more specifically, a general and repository-level Cross-Task-Instance Memory (CTIM). While existing open-source SE agents mostly rely on ReAct (Yao et al., 2023b), Reflexion (Shinn et al., 2023), or Code-Act (Wang et al., 2024), all of these reasoning and planning frameworks inefficiently discard their long-term memory after a single task instance. As repository-level understanding is pivotal for identifying all locations requiring a patch for fixing a bug, we hypothesize that SE is particularly well positioned to benefit from CTIM. For this, we build on the Experiential Learning (EL) approach ExpeL (Zhao et al., 2024), proposing a Mixture-Of-Experts (MoEs) inspired approach to create both a general-purpose and repository-level CTIM. We find that CTIM-Rover does not outperform AutoCodeRover in any configuration and thus conclude that neither ExpeL nor DoT-Bank (Lingam et al., 2024) scale to real-world SE problems. Our analysis indicates noise introduced by distracting CTIM items or exemplar trajectories as the likely source of the performance degradation.</t>
+  </si>
+  <si>
+    <t>SWE-rebench: An Automated Pipeline for Task Collection and Decontaminated Evaluation of Software Engineering Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM-based agents have shown promising capabilities in a growing range of software engineering (SWE) tasks. However, advancing this field faces two critical challenges. First, high-quality training data is scarce, especially data that reflects real-world SWE scenarios, where agents must interact with development environments, execute code and adapt behavior based on the outcomes of their actions. Existing datasets are either limited to one-shot code generation or comprise small, manually curated collections of interactive tasks, lacking both scale and diversity. Second, the lack of fresh interactive SWE tasks affects evaluation of rapidly improving models, as static benchmarks quickly become outdated due to contamination issues. To address these limitations, we introduce a novel, automated, and scalable pipeline to continuously extract real-world interactive SWE tasks from diverse GitHub repositories. Using this pipeline, we construct SWE-rebench, a public dataset comprising over 21,000 interactive Python-based SWE tasks, suitable for reinforcement learning of SWE agents at scale. Additionally, we use continuous supply of fresh tasks collected using SWE-rebench methodology to build a contamination-free benchmark for agentic software engineering. We compare results of various LLMs on this benchmark to results on SWE-bench Verified and show that performance of some language models might be inflated due to contamination issues. </t>
+  </si>
+  <si>
+    <t>Software Engineering for Self-Adaptive Robotics: A Research Agenda</t>
+  </si>
+  <si>
+    <t>Self-adaptive robotic systems are designed to operate autonomously in dynamic and uncertain environments, requiring robust mechanisms to monitor, analyse, and adapt their behaviour in real-time. Unlike traditional robotic software, which follows predefined logic, self-adaptive robots leverage artificial intelligence, machine learning, and model-driven engineering to continuously adjust to changing operational conditions while ensuring reliability, safety, and performance. This paper presents a research agenda for software engineering in self-adaptive robotics, addressing critical challenges across two key dimensions: (1) the development phase, including requirements engineering, software design, co-simulation, and testing methodologies tailored to adaptive robotic systems, and (2) key enabling technologies, such as digital twins, model-driven engineering, and AI-driven adaptation, which facilitate runtime monitoring, fault detection, and automated decision-making. We discuss open research challenges, including verifying adaptive behaviours under uncertainty, balancing trade-offs between adaptability, performance, and safety, and integrating self-adaptation frameworks like MAPE-K. By providing a structured roadmap, this work aims to advance the software engineering foundations for self-adaptive robotic systems, ensuring they remain trustworthy, efficient, and capable of handling real-world complexities.</t>
+  </si>
+  <si>
+    <t>Search-Based Software Engineering in the Landscape of AI Foundation Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Search-based software engineering (SBSE), at the intersection of artificial intelligence (AI) and software engineering, has been an active area of research for about 25 years. It has been applied to solve numerous problems across the entire software engineering lifecycle and has demonstrated its versatility in multiple domains. With the recent advancements in AI, particularly the emergence of foundation models (FMs), the evolution of SBSE alongside FMs remains undetermined. In this window of opportunity, we propose a research roadmap that articulates the current landscape of SBSE in relation to foundation models (FMs), highlights open challenges, and outlines potential research directions for advancing SBSE through its interplay with FMs. This roadmap aims to establish a forward-thinking and innovative perspective for the future of SBSE in the era of FM</t>
+  </si>
+  <si>
+    <t>Automated Testing of the GUI of a Real-Life Engineering Software using Large Language Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> One important step in software development is testing the finished product with actual users. These tests aim, among other goals, at determining unintuitive behavior of the software as it is presented to the end-user. Moreover, they aim to determine inconsistencies in the user-facing interface. They provide valuable feedback for the development of the software, but are time-intensive to conduct. In this work, we present GERALLT, a system that uses Large Language Models (LLMs) to perform exploratory tests of the Graphical User Interface (GUI) of a real-life engineering software. GERALLT automatically generates a list of potential unintuitive and inconsistent parts of the interface. We present the architecture of GERALLT and evaluate it on a real-world use case of the engineering software, which has been extensively tested by developers and users. Our res</t>
+  </si>
+  <si>
+    <t>Ten Years of Software Engineering in Society</t>
+  </si>
+  <si>
+    <t>In the international software engineering research community, the premier conference (ICSE) features since a decade a special track on the role of SE In Society (or SEIS track). In this work, we want to use the articles published in this track as a proxy or example of the research in this field, in terms of covered topics, trends, and gaps. Also, since SEIS was originally defined with a special focus on sustainability, we want to observe the evolution of the research in this respect. We conducted a mapping study of the 123 articles published in the SEIS track and among the results identified (i) trends pertaining sustainability, diversity and inclusion, and open-source software; (ii) gaps regarding concrete interventions to solve problems (e.g., workplace discrimination, the emotional well-being of developers); and (iii) a main sustainability focus in the social dimension, while the environmental dimension is the least frequently addressed. As future work, our aim is to stimulate discussion in the community and we hope to inspire replications of this work in other conference venues.</t>
+  </si>
+  <si>
+    <t>A Comprehensive Study on the Use of Word Embedding Models in Software Engineering Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word embedding (WE) techniques are advanced textual semantic representation models oriented from the natural language processing (NLP) area. Inspired by their effectiveness in facilitating various NLP tasks, more and more researchers attempt to adopt these WE models for their software engineering (SE) tasks, of which semantic representation of software artifacts such as bug reports and code snippets is the basis for further model building. However, existing studies are generally isolated from each other without comprehensive comparison and discussion. This not only makes the best practice of such cross-discipline technique adoption buried in scattered papers, but also makes us kind of blind to current progress in the semantic representation of SE artifacts. To this end, we decided to perform a comprehensive study on the use of WE models in the SE domain. 181 primary studies published in mainstream software engineering venues are collected for analysis. Several research questions related to the SE applications, the training strategy of WE models, the comparison with traditional semantic representation methods, etc., are answered. With the answers, we get a systematical view of the current practice of using WE for the SE domain, and figure out the challenges and actions in adopting or developing practical semantic representation approaches for the SE artifacts used in a series of SE tasks.</t>
+  </si>
+  <si>
+    <t>Code Graph Model (CGM): A Graph-Integrated Large Language Model for Repository-Level Software Engineering Tasks</t>
+  </si>
+  <si>
+    <t>Recent advances in Large Language Models (LLMs) have shown promise in function-level code generation, yet repository-level software engineering tasks remain challenging. Current solutions predominantly rely on proprietary LLM agents, which introduce unpredictability and limit accessibility, raising concerns about data privacy and model customization. This paper investigates whether open-source LLMs can effectively address repository-level tasks without requiring agent-based approaches. We demonstrate this is possible by enabling LLMs to comprehend functions and files within codebases through their semantic information and structural dependencies. To this end, we introduce Code Graph Models (CGMs), which integrate repository code graph structures into the LLM's attention mechanism and map node attributes to the LLM's input space using a specialized adapter. When combined with an agentless graph RAG framework, our approach achieves a 43.00% resolution rate on the SWE-bench Lite benchmark using the open-source Qwen2.5-72B model. This performance ranks first among open weight models, second among methods with open-source systems, and eighth overall, surpassing the previous best open-source model-based method by 12.33%.</t>
+  </si>
+  <si>
+    <t>Towards a Science of Causal Interpretability in Deep Learning for Software Engineering</t>
+  </si>
+  <si>
+    <t>This dissertation addresses achieving causal interpretability in Deep Learning for Software Engineering (DL4SE). While Neural Code Models (NCMs) show strong performance in automating software tasks, their lack of transparency in causal relationships between inputs and outputs limits full understanding of their capabilities. To build trust in NCMs, researchers and practitioners must explain code predictions. Associational interpretability, which identifies correlations, is often insufficient for tasks requiring intervention and change analysis. To address this, the dissertation introduces DoCode, a novel post hoc interpretability method for NCMs. DoCode uses causal inference to provide programming language-oriented explanations of model predictions. It follows a four-step pipeline: modeling causal problems using Structural Causal Models (SCMs), identifying the causal estimand, estimating effects with metrics like Average Treatment Effect (ATE), and refuting effect estimates. Its framework is extensible, with an example that reduces spurious correlations by grounding explanations in programming language properties. A case study on deep code generation across interpretability scenarios and various deep learning architectures demonstrates DoCode's benefits. Results show NCMs' sensitivity to code syntax changes and their ability to learn certain programming concepts while minimizing confounding bias. The dissertation also examines associational interpretability as a foundation, analyzing software information's causal nature using tools like COMET and TraceXplainer for traceability. It highlights the need to i</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis in Software Engineering: Evaluating Generative Pre-trained Transformers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentiment analysis plays a crucial role in understanding developer interactions, issue resolutions, and project dynamics within software engineering (SE). While traditional SE-specific sentiment analysis tools have made significant strides, they often fail to account for the nuanced and context-dependent language inherent to the domain. This study systematically evaluates the performance of bidirectional transformers, such as BERT, against generative pre-trained transformers, specifically GPT-4o-mini, in SE sentiment analysis. Using datasets from GitHub, Stack Overflow, and Jira, we benchmark the models' capabilities with fine-tuned and default configurations. The results reveal that fine-tuned GPT-4o-mini performs comparable to BERT and other bidirectional models on structured and balanced datasets like GitHub and Jira, achieving macro-averaged F1-scores of 0.93 and 0.98, respectively. However, on linguistically complex datasets with imbalanced sentiment distributions, such as Stack Overflow, the default GPT-4o-mini model exhibits superior generalization, achieving an accuracy of 85.3\% compared to the fine-tuned model's 13.1\%. These findings highlight the trade-offs between fine-tuning and leveraging pre-trained models for SE tasks. The study underscores the importance of aligning model architectures with dataset characteristics to optimize performance and proposes directions for future research in refining sentiment analysis tools tailored to the SE domain. </t>
+  </si>
+  <si>
+    <t>A Mosaic of Perspectives: Understanding Ownership in Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agile software development relies on self-organized teams, underlining the importance of individual responsibility. How developers take responsibility and build ownership are influenced by external factors such as architecture and development methods. This paper examines the existing literature on ownership in software engineering and in psychology, and argues that a more comprehensive view of ownership in software engineering has a great potential in improving software team's work. Initial positions on the issue are offered for discussion and to lay foundations for further research. </t>
+  </si>
+  <si>
+    <t>Guided Search Strategies in Non-Serializable Environments with Applications to Software Engineering Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large language models (LLMs) have recently achieved remarkable results in complex multi-step tasks, such as mathematical reasoning and agentic software engineering. However, they often struggle to maintain consistent performance across multiple solution attempts. One effective approach to narrow the gap between average-case and best-case performance is guided test-time search, which explores multiple solution paths to identify the most promising one. Unfortunately, effective search techniques (e.g. MCTS) are often unsuitable for non-serializable RL environments, such as Docker containers, where intermediate environment states cannot be easily saved and restored. We investigate two complementary search strategies applicable to such environments: 1-step lookahead and trajectory selection, both guided by a learned action-value function estimator. On the SWE-bench Verified benchmark, a key testbed for agentic software engineering, we find these methods to double the average success rate of a fine-tuned Qwen-72B model, achieving 40.8%, the new state-of-the-art for open-weights models. Additionally, we show that these techniques are transferable to more advanced closed models, yielding similar improvements with GPT-4o. </t>
+  </si>
+  <si>
+    <t>Introduction to Analytical Software Engineering Design Paradigm</t>
+  </si>
+  <si>
+    <t>As modern software systems expand in scale and complexity, the challenges associated with their modeling and formulation grow increasingly intricate. Traditional approaches often fall short in effectively addressing these complexities, particularly in tasks such as design pattern detection for maintenance and assessment, as well as code refactoring for optimization and long-term sustainability. This growing inadequacy underscores the need for a paradigm shift in how such challenges are approached and resolved. This paper presents Analytical Software Engineering (ASE), a novel design paradigm aimed at balancing abstraction, tool accessibility, compatibility, and scalability. ASE enables effective modeling and resolution of complex software engineering problems. The paradigm is evaluated through two frameworks Behavioral-Structural Sequences (BSS) and Optimized Design Refactoring (ODR), both developed in accordance with ASE principles. BSS offers a compact, language-agnostic representation of codebases to facilitate precise design pattern detection. ODR unifies artifact and solution representations to optimize code refactoring via heuristic algorithms while eliminating iterative computational overhead. By providing a structured approach to software design challenges, ASE lays the groundwork for future research in encoding and analyzing complex software metrics.</t>
+  </si>
+  <si>
+    <t>Investigating the Role of Cultural Values in Adopting Large Language Models for Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a socio-technical activity, software development involves the close interconnection of people and technology. The integration of Large Language Models (LLMs) into this process exemplifies the socio-technical nature of software development. Although LLMs influence the development process, software development remains fundamentally human-centric, necessitating an investigation of the human factors in this adoption. Thus, with this study we explore the factors influencing the adoption of LLMs in software development, focusing on the role of professionals' cultural values. Guided by the Unified Theory of Acceptance and Use of Technology (UTAUT2) and Hofstede's cultural dimensions, we hypothesized that cultural values moderate the relationships within the UTAUT2 framework. Using Partial Least Squares-Structural Equation Modelling and data from 188 software engineers, we found that habit and performance expectancy are the primary drivers of LLM adoption, while cultural values do not significantly moderate this process. These findings suggest that, by highlighting how LLMs can boost performance and efficiency, organizations can encourage their use, no matter the cultural differences. Practical steps include offering training programs to demonstrate LLM benefits, creating a supportive environment for regular use, and continuously tracking and sharing performance improvements from using LLMs. </t>
+  </si>
+  <si>
+    <t>Large Language Model-Based Agents for Software Engineering: A Survey</t>
+  </si>
+  <si>
+    <t>The recent advance in Large Language Models (LLMs) has shaped a new paradigm of AI agents, i.e., LLM-based agents. Compared to standalone LLMs, LLM-based agents substantially extend the versatility and expertise of LLMs by enhancing LLMs with the capabilities of perceiving and utilizing external resources and tools. To date, LLM-based agents have been applied and shown remarkable effectiveness in Software Engineering (SE). The synergy between multiple agents and human interaction brings further promise in tackling complex real-world SE problems. In this work, we present a comprehensive and systematic survey on LLM-based agents for SE. We collect 106 papers and categorize them from two perspectives, i.e., the SE and agent perspectives. In addition, we discuss open challenges and future directions in this critical domain. The repository of this survey is at https://github.com/FudanSELab/Agent4SE-Paper-List.</t>
+  </si>
+  <si>
+    <t>The Impact of Generative AI-Powered Code Generation Tools on Software Engineer Hiring: Recruiters' Experiences, Perceptions, and Strategies</t>
+  </si>
+  <si>
+    <t>The rapid advancements in Generative AI (GenAI) tools, such as ChatGPT and GitHub Copilot, are transforming software engineering by automating code generation tasks. While these tools improve developer productivity, they also present challenges for organizations and hiring professionals in evaluating software engineering candidates' true abilities and potential. Although there is existing research on these tools in both industry and academia, there is a lack of research on how these tools specifically affect the hiring process. Therefore, this study aims to explore recruiters' experiences and perceptions regarding GenAI-powered code generation tools, as well as their challenges and strategies for evaluating candidates. Findings from our survey of 32 industry professionals indicate that although most participants are familiar with such tools, the majority of organizations have not adjusted their candidate evaluation methods to account for candidates' use/knowledge of these tools. There are mixed opinions on whether candidates should be allowed to use these tools during interviews, with many participants valuing candidates who can effectively demonstrate their skills in using these tools. Additionally, most participants believe that it is important to incorporate GenAI-powered code generation tools into computer science curricula and mention the key risks and benefits of doing so</t>
+  </si>
+  <si>
+    <t>Chain-of-Experts (CoE): Reverse Engineering Software Bills of Materials for JavaScript Application Bundles through Code Clone Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Software Bill of Materials (SBoM) is a detailed inventory of all components, libraries, and modules in a software artifact, providing traceability throughout the software supply chain. With the increasing popularity of JavaScript in software engineering due to its dynamic syntax and seamless supply chain integration, the exposure to vulnerabilities and attacks has risen significantly. A JavaScript application bundle, which is a consolidated, symbol-stripped, and optimized assembly of code for deployment purpose. Generating a SBoM from a JavaScript application bundle through a reverse-engineering process ensures the integrity, security, and compliance of the supplier's software release, even without access to the original dependency graphs. This paper presents the first study on SBoM generation for JavaScript application bundles. We identify three key challenges for this task, i.e., nested code scopes, extremely long sequences, and large retrieval spaces. To address these challenges, we introduce Chain-of-Experts (CoE), a multi-task deep learning model designed to generate SBoMs through three tasks: code segmentation, code classification, and code clone retrieval. We evaluate CoE against individual task-specific solutions on 500 web application bundles with over 66,000 dependencies. Our experimental results demonstrate that CoE offers competitive outcomes with less training and inference time when compared with combined individual task-specific solutions. Consequently, CoE provides the first scalable, efficient, and end-to-end solution for the SBoM generation of real-world JavaScript application bundles. </t>
+  </si>
+  <si>
+    <t>A Systematic Mapping Study of Crowd Knowledge Enhanced Software Engineering Research Using Stack Overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Developers continuously interact in crowd-sourced community-based question-answer (Q&amp;A) sites. Reportedly, 30% of all software professionals visit the most popular Q&amp;A site StackOverflow (SO) every day. Software engineering (SE) research studies are also increasingly using SO data. To find out the trend, implication, impact, and future research potential utilizing SO data, a systematic mapping study needs to be conducted. Following a rigorous reproducible mapping study approach, from 18 reputed SE journals and conferences, we collected 384 SO-based research articles and categorized them into 10 facets (i.e., themes). We found that SO contributes to 85% of SE research compared with popular Q&amp;A sites such as Quora, and Reddit. We found that 18 SE domains directly benefited from SO data whereas Recommender Systems, and API Design and Evolution domains use SO data the most (15% and 16% of all SO-based research studies, respectively). API Design and Evolution, and Machine Learning with/for SE domains have consistent upward publication. Deep Learning Bug Analysis and Code Cloning research areas have the highest potential research impact recently. With the insights, recommendations, and facet-based categorized paper list from this mapping study, SE researchers can find potential research areas according to their interest to utilize large-scale SO data. </t>
+  </si>
+  <si>
+    <t>Crossover Designs in Software Engineering Experiments: Review of the State of Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experimentation is an essential method for causal inference in any empirical discipline. Crossover-design experiments are common in Software Engineering (SE) research. In these, subjects apply more than one treatment in different orders. This design increases the amount of obtained data and deals with subject variability but introduces threats to internal validity like the learning and carryover effect. Vegas et al. reviewed the state of practice for crossover designs in SE research and provided guidelines on how to address its threats during data analysis while still harnessing its benefits. In this paper, we reflect on the impact of these guidelines and review the state of analysis of crossover design experiments in SE publications between 2015 and March 2024. To this end, by conducting a forward snowballing of the guidelines, we survey 136 publications reporting 67 crossover-design experiments and evaluate their data analysis against the provided guidelines. The results show that the validity of data analyses has improved compared to the original state of analysis. Still, despite the explicit guidelines, only 29.5% of all threats to validity were addressed properly. While the maturation and the optimal sequence threats are properly addressed in 35.8% and 38.8% of all studies in our sample respectively, the carryover threat is only modeled in about 3% of the observed cases. The lack of adherence to the analysis guidelines threatens the validity of the conclusions drawn from crossover design experiments </t>
+  </si>
+  <si>
+    <t>Diversity Empowers Intelligence: Integrating Expertise of Software Engineering Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large language model (LLM) agents have shown great potential in solving real-world software engineering (SWE) problems. The most advanced open-source SWE agent can resolve over 27% of real GitHub issues in SWE-Bench Lite. However, these sophisticated agent frameworks exhibit varying strengths, excelling in certain tasks while underperforming in others. To fully harness the diversity of these agents, we propose DEI (Diversity Empowered Intelligence), a framework that leverages their unique expertise. DEI functions as a meta-module atop existing SWE agent frameworks, managing agent collectives for enhanced problem-solving. Experimental results show that a DEI-guided committee of agents is able to surpass the best individual agent's performance by a large margin. For instance, a group of open-source SWE agents, with a maximum individual resolve rate of 27.3% on SWE-Bench Lite, can achieve a 34.3% resolve rate with DEI, making a 25% improvement and beating most closed-source solutions. Our best-performing group excels with a 55% resolve rate, securing the highest ranking on SWE-Bench Lite. Our findings contribute to the growing body of research on collaborative AI systems and their potential to solve complex software engineering challenges</t>
+  </si>
+  <si>
+    <t>A pragmatic look at education and training of software test engineers: Further cooperation of academia and industry is needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alongside software testing education in universities, a great extent of effort and resources are spent on software-testing training activities in industry. For example, there are several international certification schemes in testing, such as those provided by the International Software Testing Qualifications Board (ISTQB), which have been issued to more than 914K testers so far. To train the highly qualified test engineers of tomorrow, it is important for both university educators and trainers in industry to be aware of the status of software testing education in academia versus its training in industry, to analyze the relationships of these two approaches, and to assess ways on how to improve the education / training landscape. For that purpose, this paper provides a pragmatic overview of the issue, presents several recommendations, and hopes to trigger further discussions in the community, between industry and academia, on how to further improve the status-quo, and to find further best practices for more effective education and training of software testers. The paper is based on combined ~40 years of the two authors' technical experience in test engineering, and their ~30 years of experience in providing testing education and training in more than six countries. </t>
+  </si>
+  <si>
+    <t>Can LLMs Replace Manual Annotation of Software Engineering Artifacts?</t>
+  </si>
+  <si>
+    <t>Experimental evaluations of software engineering innovations, e.g., tools and processes, often include human-subject studies as a component of a multi-pronged strategy to obtain greater generalizability of the findings. However, human-subject studies in our field are challenging, due to the cost and difficulty of finding and employing suitable subjects, ideally, professional programmers with varying degrees of experience. Meanwhile, large language models (LLMs) have recently started to demonstrate human-level performance in several areas. This paper explores the possibility of substituting costly human subjects with much cheaper LLM queries in evaluations of code and code-related artifacts. We study this idea by applying six state-of-the-art LLMs to ten annotation tasks from five datasets created by prior work, such as judging the accuracy of a natural language summary of a method or deciding whether a code change fixes a static analysis warning. Our results show that replacing some human annotation effort with LLMs can produce inter-rater agreements equal or close to human-rater agreement. To help decide when and how to use LLMs in human-subject studies, we propose model-model agreement as a predictor of whether a given task is suitable for LLMs at all, and model confidence as a means to select specific samples where LLMs can safely replace human annotators. Overall, our work is the first step toward mixed human-LLM evaluations in software engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Establishing Software Engineering Design Competence with Soft Skills  </t>
+  </si>
+  <si>
+    <t>For a long time, it has been recognized that the software industry has a demand for students who are well grounded in design competencies and who are ready to contribute to a project with little additional training. In response to the industry needs, an engineering design course has been developed for senior level students enrolled in the software engineering program in Canada. The goals of the course are to provide a realistic design experience, introduce students to industry culture, improve their time management skills, challenge them technically and intellectually, improve their communication skills, raise student level of professionalism, hone their soft skills, and raise awareness of human factors in software engineering. This work discusses the details of how this design course has been developed and delivered, and the learning outcomes that has been obtained.</t>
+  </si>
+  <si>
+    <t>From LLMs to LLM-based Agents for Software Engineering: A Survey of Current, Challenges and Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> With the rise of large language models (LLMs), researchers are increasingly exploring their applications in var ious vertical domains, such as software engineering. LLMs have achieved remarkable success in areas including code generation and vulnerability detection. However, they also exhibit numerous limitations and shortcomings. LLM-based agents, a novel tech nology with the potential for Artificial General Intelligence (AGI), combine LLMs as the core for decision-making and action-taking, addressing some of the inherent limitations of LLMs such as lack of autonomy and self-improvement. Despite numerous studies and surveys exploring the possibility of using LLMs in software engineering, it lacks a clear distinction between LLMs and LLM based agents. It is still in its early stage for a unified standard and benchmarking to qualify an LLM solution as an LLM-based agent in its domain. In this survey, we broadly investigate the current practice and solutions for LLMs and LLM-based agents for software engineering. In particular we summarise six key topics: requirement engineering, code generation, autonomous decision-making, software design, test generation, and software maintenance. We review and differentiate the work of LLMs and LLM-based agents from these six topics, examining their differences and similarities in tasks, benchmarks, and evaluation metrics. Finally, we discuss the models and benchmarks used, providing a comprehensive analysis of their applications and effectiveness in software engineering. We anticipate this work will shed some lights on pushing the boundaries of LLM-based agents in software engineering for future research. </t>
+  </si>
+  <si>
+    <t>Teaching Survey Research in Software Engineering</t>
+  </si>
+  <si>
+    <t>In this chapter, we provide advice on how to effectively teach survey research based on lessons learned from several international teaching experiences on the topic and from conducting large-scale surveys published at various scientific conferences and journals. First, we provide teachers with a potential syllabus for teaching survey research, including learning objectives, lectures, and examples of practical assignments. Thereafter, we provide actionable advice on how to teach the topics related to each learning objective, including survey design, sampling, data collection, statistical and qualitative analysis, threats to validity and reliability, and ethical considerations. The chapter is complemented by online teaching resources, including slides covering an entire course.</t>
+  </si>
+  <si>
+    <t>Generative AI in Evidence-Based Software Engineering: A White Paper</t>
+  </si>
+  <si>
+    <t>Context. In less than a year practitioners and researchers witnessed a rapid and wide implementation of Generative Artificial Intelligence. The daily availability of new models proposed by practitioners and researchers has enabled quick adoption. Textual GAIs capabilities enable researchers worldwide to explore new generative scenarios simplifying and hastening all timeconsuming text generation and analysis tasks. Motivation. The exponentially growing number of publications in our field with the increased accessibility to information due to digital libraries makes conducting systematic literature reviews and mapping studies an effort and timeinsensitive task Stemmed from this challenge we investigated and envisioned the role of GAIs in evidencebased software engineering. Future Directions. Based on our current investigation we will follow up the vision with the creation and empirical validation of a comprehensive suite of models to effectively support EBSE researchers</t>
+  </si>
+  <si>
+    <t>Agile Minds, Innovative Solutions, and Industry-Academia Collaboration: Lean R&amp;D Meets Problem-Based Learning in Software Engineering Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software Engineering (SE) education constantly seeks to bridge the gap between academic knowledge and industry demands, with active learning methods like Problem-Based Learning (PBL) gaining prominence. Despite these efforts, recent graduates struggle to align skills with industry needs. Recognizing the relevance of Industry-Academia Collaboration (IAC), Lean R&amp;D has emerged as a successful agile-based research and development approach, emphasizing business and software development synergy. [Goal] This paper aims to extend Lean R&amp;D with PBL principles, evaluating its application in an educational program designed by ExACTa PUC- Rio for Americanas S.A., a large Brazilian retail company. [Method] The educational program engaged 40 part-time students receiving lectures and mentoring while working on real problems, coordinators and mentors, and company stakeholders in industry projects. Empirical evaluation, through a case study approach, utilized structured questionnaires based on the Technology Acceptance Model (TAM). [Results] Stakeholders were satisfied with Lean R&amp;D PBL for problem-solving. Students reported increased knowledge proficiency and perceived working on real problems as contributing the most to their learning. [Conclusion] This research contributes to academia by sharing Lean R&amp;D PBL as an educational IAC approach. For industry, we discuss the implementation of this proposal in an IAC program that promotes workforce skill development and innovative solutions.</t>
+  </si>
+  <si>
+    <t>Towards Effective Collaboration between Software Engineers and Data Scientists developing Machine Learning-Enabled Systems</t>
+  </si>
+  <si>
+    <t>Incorporating Machine Learning (ML) into existing systems is a demand that has grown among several organizations. However, the development of ML-enabled systems encompasses several social and technical challenges, which must be addressed by actors with different fields of expertise working together. This paper has the objective of understanding how to enhance the collaboration between two key actors in building these systems: software engineers and data scientists. We conducted two focus group sessions with experienced data scientists and software engineers working on real-world ML-enabled systems to assess the relevance of different recommendations for specific technical tasks. Our research has found that collaboration between these actors is important for effectively developing ML-enabled systems, especially when defining data access and ML model deployment. Participants provided concrete examples of how recommendations depicted in the literature can benefit collaboration during different tasks. For example, defining clear responsibilities for each team member and creating concise documentation can improve communication and overall performance. Our study contributes to a better understanding of how to foster effective collaboration between software engineers and data scientists creating ML-enabled systems.</t>
+  </si>
+  <si>
+    <t>Are Educational Escape Rooms More Effective Than Traditional Lectures for Teaching Software Engineering? A Randomized Controlled Trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This article analyzes the learning effectiveness of a virtual educational escape room for teaching software engineering and compares this activity with traditional teaching through a randomized controlled trial. Background: Educational escape rooms have been used across a wide variety of disciplines at all levels of education and they are becoming increasingly popular among teachers. Nevertheless, there is a clear general need for more robust empirical evidence on the learning effectiveness of these novel activities and, particularly, on their application in software engineering education. Research Questions: Is game-based learning using educational escape rooms more effective than traditional lectures for teaching software engineering? What are the perceptions of software engineering students toward game-based learning using educational escape rooms? Methodology: The study presented in this article is a randomized controlled trial with a pre-and post-test design that was completed by a total of 326 software engineering students. The 164 students belonging to the experimental group learned software modeling by playing an educational escape room whereas the 162 students belonging to the control group learned the same subject matter through a traditional lecture. Findings: The results of the randomized controlled trial show that the students who learned software modeling through the educational escape room had very positive perceptions toward this activity, significantly increased their knowledge, and outperformed those students who learned through a traditional lecture in terms of knowledge acquisition. </t>
+  </si>
+  <si>
+    <t>A Transformer-based Approach for Augmenting Software Engineering Chatbots Datasets</t>
+  </si>
+  <si>
+    <t>The adoption of chatbots into software development tasks has become increasingly popular among practitioners, driven by the advantages of cost reduction and acceleration of the software development process. Chatbots understand users' queries through the Natural Language Understanding component (NLU). To yield reasonable performance, NLUs have to be trained with extensive, high-quality datasets, that express a multitude of ways users may interact with chatbots. However, previous studies show that creating a high-quality training dataset for software engineering chatbots is expensive in terms of both resources and time. Aims: Therefore, in this paper, we present an automated transformer-based approach to augment software engineering chatbot datasets. Method: Our approach combines traditional natural language processing techniques with the BART transformer to augment a dataset by generating queries through synonym replacement and paraphrasing. We evaluate the impact of using the augmentation approach on the Rasa NLU's performance using three software engineering datasets. Results: Overall, the augmentation approach shows promising results in improving the Rasa's performance, augmenting queries with varying sentence structures while preserving their original semantics. Furthermore, it increases Rasa's confidence in its intent classification for the correctly classified intents. Conclusions: We believe that our study helps practitioners improve the performance of their chatbots and guides future research to propose augmentation techniques for SE chatbots.</t>
+  </si>
+  <si>
+    <t>A Systematic Literature Review on Task Recommendation Systems for Crowdsourced Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Crowdsourced Software Engineering (CSE) offers outsourcing work to software practitioners by leveraging a global online workforce. However, these software practitioners struggle to identify suitable tasks due to the variety of options available. Hence, there have been a growing number of studies on introducing recommendation systems to recommend CSE tasks to software practitioners. The goal of this study is to analyze the existing CSE task recommendation systems, investigating their extracted data, recommendation methods, key advantages and limitations, recommended task types, the use of human factors in recommendations, popular platforms, and features used to make recommendations. This SLR was conducted according to the Kitchenham and Charters' guidelines. We used both manual and automatic search strategies without putting any time limitation for searching the relevant papers. We selected 65 primary studies for data extraction, analysis, and synthesis based on our predefined inclusion and exclusion criteria. From the results of the data analysis, we classified the extracted data into four categories based on the data extraction source, categorized the proposed recommendation systems to fit into a taxonomy, and identified the key advantages and limitations of these systems. Our results revealed that human factors play a major role in CSE task recommendation. Further, we identified five popular task types recommended, popular platforms, and their features used in task recommendation. We also provided recommendations for future research directions. This SLR provides insights into current trends, gaps, and future research directions in CSE task recommendation systems </t>
+  </si>
+  <si>
+    <t>With Great Power Comes Great Responsibility: The Role of Software Engineers</t>
+  </si>
+  <si>
+    <t>The landscape of software engineering is evolving rapidly amidst the digital transformation and the ascendancy of AI, leading to profound shifts in the role and responsibilities of software engineers. This evolution encompasses both immediate changes, such as the adoption of Language Model-based approaches in coding, and deeper shifts driven by the profound societal and environmental impacts of technology. Despite the urgency, there persists a lag in adapting to these evolving roles. By fostering ongoing discourse and reflection on Software Engineers role and responsibilities, this vision paper seeks to cultivate a new generation of software engineers equipped to navigate the complexities and ethical considerations inherent in their evolving profession.</t>
+  </si>
+  <si>
+    <t>Foundation Model Engineering: Engineering Foundation Models Just as Engineering Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By treating data and models as the source code, Foundation Models (FMs) become a new type of software. Mirroring the concept of software crisis, the increasing complexity of FMs making FM crisis a tangible concern in the coming decade, appealing for new theories and methodologies from the field of software engineering. In this paper, we outline our vision of introducing Foundation Model (FM) engineering, a strategic response to the anticipated FM crisis with principled engineering methodologies. FM engineering aims to mitigate potential issues in FM development and application through the introduction of declarative, automated, and unified programming interfaces for both data and model management, reducing the complexities involved in working with FMs by providing a more structured and intuitive process for developers. Through the establishment of FM engineering, we aim to provide a robust, automated, and extensible framework that addresses the imminent challenges, and discovering new research opportunities for the software engineering field. </t>
+  </si>
+  <si>
+    <t>Integrating Human-Centric Approaches into Undergraduate Software Engineering Education: A Scoping Review and Curriculum Analysis in the Australian Context</t>
+  </si>
+  <si>
+    <t>Human-Centric Software Engineering (HCSE) refers to the software engineering (SE) processes that put human needs and requirements as core practice throughout the software development life cycle. A large majority of software projects fail to cater to human needs and consequently run into budget, delivery, and usability issues. To support human-centric software engineering practices, it is important for universities to train their students on how to consider human needs. But what topics from HCSE should be provided in the undergraduate curriculum? Curriculum guidelines for software engineering are available, however do not represent update to date considerations for human-factors. To address this issue, this paper presents a scoping review to identify the topics and curriculum approaches suitable for teaching HCSE to undergraduate software engineering students. The scoping review was conducted according to the protocol by PRISMA-ScR (Preferred Reporting Items for Systematic reviews and Meta-Analyses extension for Scoping Reviews). Through PRISMA-ScR, a total of 36 conference or journal papers were identified as viable for analysis,with 5 common themes found that describe topics and curriculum approaches relevant for teaching software engineering. Using the outcomes of the scoping review, this paper also analyses the Australian Software Engineering curriculum to understand the extent at which human centred software engineering topics are scaffolded into course structures. This paper concludes by suggesting topic scaffolding for the undergraduate curriculum that aligns with the software engineering process. Overall, by providing a focus on HCSE topics and curriculum approaches, the education of HCSE among current and future software engineers can increase, leading to long-term impact on the success of software projects for all stakeholder</t>
+  </si>
+  <si>
+    <t>Employing Software Diversity in Cloud Microservices to Engineer Reliable and Performant Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the ever-shifting landscape of software engineering, we recognize the need for adaptation and evolution to maintain system dependability. As each software iteration potentially introduces new challenges, from unforeseen bugs to performance anomalies, it becomes paramount to understand and address these intricacies to ensure robust system operations during the lifetime. This work proposes employing software diversity to enhance system reliability and performance simultaneously. A cornerstone of our work is the derivation of a reliability metric. This metric encapsulates the reliability and performance of each software version under adverse conditions. Using the calculated reliability score, we implemented a dynamic controller responsible for adjusting the population of each software version. The goal is to maintain a higher replica count for more reliable versions while preserving the diversity of versions as much as possible. This balance is crucial for ensuring not only the reliability but also the performance of the system against a spectrum of potential failures. In addition, we designed and implemented a diversity-aware autoscaling algorithm that maintains the reliability and performance of the system at the same time and at any scale. Our extensive experiments on realistic cloud microservice-based applications show the effectiveness of the proposed approach in this paper in promoting both reliability and performance. </t>
+  </si>
+  <si>
+    <t>Ten Years of Teaching Empirical Software Engineering in the context of Energy-efficient Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In this chapter we share our experience in running ten editions of the Green Lab course at the Vrije Universiteit Amsterdam, the Netherlands. The course is given in the Software Engineering and Green IT track of the Computer Science Master program of the VU. The course takes place every year over a 2-month period and teaches Computer Science students the fundamentals of Empirical Software Engineering in the context of energy-efficient software. The peculiarity of the course is its research orientation: at the beginning of the course the instructor presents a catalog of scientifically relevant goals, and each team of students signs up for one of them and works together for 2 months on their own experiment for achieving the goal. Each team goes over the classic steps of an empirical study, starting from a precise formulation of the goal and research questions to context definition, selection of experimental subjects and objects, definition of experimental variables, experiment execution, data analysis, and reporting. Over the years, the course became well-known within the Software Engineering community since it led to several scientific studies that have been published at various scientific conferences and journals. Also, students execute their experiments using \textit{open-source tools}, which are developed and maintained by researchers and other students within the program, thus creating a virtuous community of learners where students exchange ideas, help each other, and learn how to collaboratively contribute to open-source projects in a safe environment. </t>
+  </si>
+  <si>
+    <t>Teaching Research Design in Software Engineering</t>
+  </si>
+  <si>
+    <t>In the dynamic field of Software Engineering (SE), where practice is constantly evolving and adapting to new technologies, conducting research is a daunting quest. This poses a challenge for researchers: how to stay relevant and effective in their studies? Empirical Software Engineering (ESE) has emerged as a contending force aiming to critically evaluate and provide knowledge that informs practice in adopting new technologies. Empirical research requires a rigorous process of collecting and analyzing data to obtain evidence-based findings. Challenges to this process are numerous, and many researchers, novice and experienced, found difficulties due to many complexities involved in designing their research. The core of this chapter is to teach foundational skills in research design, essential for educating software engineers and researchers in ESE. It focuses on developing a well-structured research design, which includes defining a clear area of investigation, formulating relevant research questions, and choosing appropriate methodologies. While the primary focus is on research design, this chapter also covers aspects of research scoping and selecting research methods. This approach prepares students to handle the complexities of the ever-changing technological landscape in SE, making it a critical component of their educational curriculum.</t>
+  </si>
+  <si>
+    <t>Action Research with Industrial Software Engineering -- An Educational Perspective</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Action research provides the opportunity to explore the usefulness and usability of software engineering methods in industrial settings, and makes it possible to develop methods, tools and techniques with software engineering practitioners. However, as the research moves beyond the observational approach, it requires a different kind of interaction with the software development organisation. This makes action research a challenging endeavour, and it makes it difficult to teach action research through a course that goes beyond explaining the principles. This chapter is intended to support learning and teaching action research, by providing a rich set of examples, and identifying tools that we found helpful in our action research projects. The core of this chapter focusses on our interaction with the participating developers and domain experts, and the organisational setting. This chapter is structured around a set of challenges that reoccurred in the action research projects in which the authors participated. Each section is accompanied by a toolkit that presents related techniques and tools. The exercises are designed to explore the topics, and practise using the tools and techniques presented. We hope the material in this chapter encourages researchers who are new to action research to further explore this promising opportunity.</t>
+  </si>
+  <si>
+    <t>Teaching and Learning Ethnography for Software Engineering Contexts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ethnography has become one of the established methods for empirical research on software engineering. Although there is a wide variety of introductory books available, there has been no material targeting software engineering students particularly, until now. In this chapter we provide an introduction to teaching and learning ethnography for faculty teaching ethnography to software engineering graduate students and for the students themselves of such courses. The contents of the chapter focuses on what we think is the core basic knowledge for newbies to ethnography as a research method. We complement the text with proposals for exercises, tips for teaching, and pitfalls that we and our students have experienced. The chapter is designed to support part of a course on empirical software engineering and provides pointers and literature for further reading. </t>
+  </si>
+  <si>
+    <t>Agentless: Demystifying LLM-based Software Engineering Agents</t>
+  </si>
+  <si>
+    <t>Recent advancements in large language models (LLMs) have significantly advanced the automation of software development tasks, including code synthesis, program repair, and test generation. More recently, researchers and industry practitioners have developed various autonomous LLM agents to perform end-to-end software development tasks. These agents are equipped with the ability to use tools, run commands, observe feedback from the environment, and plan for future actions. However, the complexity of these agent-based approaches, together with the limited abilities of current LLMs, raises the following question: Do we really have to employ complex autonomous software agents? To attempt to answer this question, we build Agentless -- an agentless approach to automatically solve software development problems. Compared to the verbose and complex setup of agent-based approaches, Agentless employs a simplistic three-phase process of localization, repair, and patch validation, without letting the LLM decide future actions or operate with complex tools. Our results on the popular SWE-bench Lite benchmark show that surprisingly the simplistic Agentless is able to achieve both the highest performance (32.00%, 96 correct fixes) and low cost ($0.70) compared with all existing open-source software agents! Furthermore, we manually classified the problems in SWE-bench Lite and found problems with exact ground truth patch or insufficient/misleading issue descriptions. As such, we construct SWE-bench Lite-S by excluding such problematic issues to perform more rigorous evaluation and comparison. Our work highlights the current overlooked potential of a simple, interpretable technique in autonomous software development. We hope Agentless will help reset the baseline, starting point, and horizon for autonomous software agents, and inspire future work along this crucial direction.</t>
+  </si>
+  <si>
+    <t>Please do not go: understanding turnover of software engineers from different perspectives</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Turnover consists of moving into and out of professional employees in the company in a given period. Such a phenomenon significantly impacts the software industry since it generates knowledge loss, delays in the schedule, and increased costs in the final project. Despite the efforts made by researchers and professionals to minimize the turnover, more studies are needed to understand the motivation that drives Software Engineers to leave their jobs and the main strategies CEOs adopt to retain these professionals in software development companies. In this paper, we contribute a mixed methods study involving semi-structured interviews with Software Engineers and CEOs to obtain a wider opinion of these professionals about turnover and a subsequent validation survey with additional software engineers to check and review the insights from interviews. In studying such aspects, we identified 19 different reasons for software engineers' turnover and 18 more efficient strategies used in the software development industry to reduce it. Our findings provide several implications for industry and academia, which can drive future research.</t>
+  </si>
+  <si>
+    <t>Teaching Theorizing in Software Engineering Research</t>
+  </si>
+  <si>
+    <t>This chapter seeks to support software engineering (SE) researchers and educators in teaching the importance of theory as well as the theorizing process. Drawing on insights from other fields, the chapter presents 12 intermediate products of theorizing and what they mean in an SE context. These intermediate products serve different roles: some are theory products to frame research studies, some are theory generators, and others are components of theory. Whereas the SE domain doesn't have many theories of its own, these intermediate products of theorizing can be found widely. The chapter aims to help readers to recognize these intermediate products, their role, and how they can help in the theorizing process within SE research. To illustrate their utility, the chapter then applies the set of intermediate theorizing products to the software architecture research field. The chapter ends with a suggested structure for a 12-week course on theorizing in SE which can be readily adapted by educato</t>
+  </si>
+  <si>
+    <t>Teaching Software Metrology: The Science of Measurement for Software Engineering</t>
+  </si>
+  <si>
+    <t>While the methodological rigor of computing research has improved considerably in the past two decades, quantitative software engineering research is hampered by immature measures and inattention to theory. Measurement-the principled assignment of numbers to phenomena-is intrinsically difficult because observation is predicated upon not only theoretical concepts but also the values and perspective of the research. Despite several previous attempts to raise awareness of more sophisticated approaches to measurement and the importance of quantitatively assessing reliability and validity, measurement issues continue to be widely ignored. The reasons are unknown, but differences in typical engineering and computer science graduate training programs (compared to psychology and management, for example) are involved. This chapter therefore reviews key concepts in the science of measurement and applies them to software engineering research. A series of exercises for applying important measurement concepts to the reader's research are included, and a sample dataset for the reader to try some of the statistical procedures mentioned is provided</t>
+  </si>
+  <si>
+    <t>A Systematic Literature Review on the Use of Machine Learning in Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software engineering (SE) is a dynamic field that involves multiple phases all of which are necessary to develop sustainable software systems. Machine learning (ML), a branch of artificial intelligence (AI), has drawn a lot of attention in recent years thanks to its ability to analyze massive volumes of data and extract useful patterns from data. Several studies have focused on examining, categorising, and assessing the application of ML in SE processes. We conducted a literature review on primary studies to address this gap. The study was carried out following the objective and the research questions to explore the current state of the art in applying machine learning techniques in software engineering processes. The review identifies the key areas within software engineering where ML has been applied, including software quality assurance, software maintenance, software comprehension, and software documentation. It also highlights the specific ML techniques that have been leveraged in these domains, such as supervised learning, unsupervised learning, and deep learning. Keywords: machine learning, deep learning, software engineering, natural language processing, source code </t>
+  </si>
+  <si>
+    <t>MASAI: Modular Architecture for Software-engineering AI Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A common method to solve complex problems in software engineering, is to divide the problem into multiple sub-problems. Inspired by this, we propose a Modular Architecture for Software-engineering AI (MASAI) agents, where different LLM-powered sub-agents are instantiated with well-defined objectives and strategies tuned to achieve those objectives. Our modular architecture offers several advantages: (1) employing and tuning different problem-solving strategies across sub-agents, (2) enabling sub-agents to gather information from different sources scattered throughout a repository, and (3) avoiding unnecessarily long trajectories which inflate costs and add extraneous context. MASAI enabled us to achieve the highest performance (28.33% resolution rate) on the popular and highly challenging SWE-bench Lite dataset consisting of 300 GitHub issues from 11 Python repositories. We conduct a comprehensive evaluation of MASAI relative to other agentic methods and analyze the effects of our design decisions and their contribution to the success of MASAI. </t>
+  </si>
+  <si>
+    <t>The Rise and Fall(?) of Software Engineering</t>
+  </si>
+  <si>
+    <t>Over the last ten years, the realm of Artificial Intelligence (AI) has experienced an explosion of revolutionary breakthroughs, transforming what seemed like a far-off dream into a reality that is now deeply embedded in our everyday lives. AI's widespread impact is revolutionizing virtually all aspects of human life, and software engineering (SE) is no exception. As we explore this changing landscape, we are faced with questions about what the future holds for SE and how AI will reshape the roles, duties, and methodologies within the field. The introduction of these groundbreaking technologies highlights the inevitable shift towards a new paradigm, suggesting a future where AI's capabilities may redefine the boundaries of SE, potentially even more than human input. In this paper, we aim at outlining the key elements that, based on our expertise, are vital for the smooth integration of AI into SE, all while preserving the intrinsic human creativity that has been the driving force behind the field. First, we provide a brief description of SE and AI evolution. Afterward, we delve into the intricate interplay between AI-driven automation and human innovation, exploring how these two components can work together to advance SE practices to new methods and standards.</t>
+  </si>
+  <si>
+    <t>Some things never change: how far generative AI can really change software engineering practice</t>
+  </si>
+  <si>
+    <t>Generative Artificial Intelligence (GenAI) has become an emerging technology with the availability of several tools that could impact Software Engineering (SE) activities. As any other disruptive technology, GenAI led to the speculation that its full potential can deeply change SE. However, an overfocus on improving activities for which GenAI is more suitable could negligent other relevant areas of the process. In this paper, we aim to explore which SE activities are not expected to be profoundly changed by GenAI. To achieve this goal, we performed a survey with SE practitioners to identify their expectations regarding GenAI in SE, including impacts, challenges, ethical issues, and aspects they do not expect to change. We compared our results with previous roadmaps proposed in SE literature. Our results show that although practitioners expect an increase in productivity, coding, and process quality, they envision that some aspects will not change, such as the need for human expertise, creativity, and project management. Our results point to SE areas for which GenAI is probably not so useful, and future research could tackle them to improve SE practice.</t>
+  </si>
+  <si>
+    <t>Building Software Engineering Capacity through a University Open Source Program Office</t>
+  </si>
+  <si>
+    <t>This work introduces an innovative program for training the next generation of software engineers within university settings, addressing the limitations of traditional software engineering courses. Initial program costs were significant, totaling $551,420 in direct expenditures to pay for program staff salaries and benefits over two years. We present a strategy for reducing overall costs and establishing sustainable funding sources to perpetuate the program, which has yielded educational, research, professional, and societal benefits.</t>
+  </si>
+  <si>
+    <t>Teaching Literature Reviewing for Software Engineering Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The goal of this chapter is to support teachers in holistically introducing graduate students to literature reviews, with a particular focus on secondary research. It provides an overview of the overall literature review process and the different types of literature review before diving into guidelines for selecting and conducting different types of literature review. The chapter also provides recommendations for evaluating the quality of existing literature reviews and concludes with a summary of our learning goals and how the chapter supports teachers in addressing them.</t>
+  </si>
+  <si>
+    <t>Qualitative Data Analysis in Software Engineering: Techniques and Teaching Insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software repositories are rich sources of qualitative artifacts, including source code comments, commit messages, issue descriptions, and documentation. These artifacts offer many interesting insights when analyzed through quantitative methods, as outlined in the chapter on mining software repositories. This chapter shifts the focus towards interpreting these artifacts using various qualitative data analysis techniques. We introduce qualitative coding as an iterative process, which is crucial not only for educational purposes but also to enhance the credibility and depth of research findings. Various coding methods are discussed along with the strategic design of a coding guide to ensure consistency and accuracy in data interpretation. The chapter also discusses quality assurance in qualitative data analysis, emphasizing principles such as credibility, transferability, dependability, and confirmability. These principles are vital to ensure that the findings are robust and can be generalized in different contexts. By sharing best practices and lessons learned, we aim to equip all readers with the tools necessary to conduct rigorous qualitative research in the field of software engineering. </t>
+  </si>
+  <si>
+    <t>A Software Engineering Perspective on Testing Large Language Models: Research, Practice, Tools and Benchmarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large Language Models (LLMs) are rapidly becoming ubiquitous both as stand-alone tools and as components of current and future software systems. To enable usage of LLMs in the high-stake or safety-critical systems of 2030, they need to undergo rigorous testing. Software Engineering (SE) research on testing Machine Learning (ML) components and ML-based systems has systematically explored many topics such as test input generation and robustness. We believe knowledge about tools, benchmarks, research and practitioner views related to LLM testing needs to be similarly organized. To this end, we present a taxonomy of LLM testing topics and conduct preliminary studies of state of the art and practice approaches to research, open-source tools and benchmarks for LLM testing, mapping results onto this taxonomy. Our goal is to identify gaps requiring more research and engineering effort and inspire a clearer communication between LLM practitioners and the SE research community. </t>
+  </si>
+  <si>
+    <t>The Future of Software Engineering in an AI-Driven World</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A paradigm shift is underway in Software Engineering, with AI systems such as LLMs gaining increasing importance for improving software development productivity. This trend is anticipated to persist. In the next five years, we will likely see an increasing symbiotic partnership between human developers and AI. The Software Engineering research community cannot afford to overlook this trend; we must address the key research challenges posed by the integration of AI into the software development process. In this paper, we present our vision of the future of software development in an AI-Driven world and explore the key challenges that our research community should address to realize this vision</t>
+  </si>
+  <si>
+    <t>Software Engineering for Collective Cyber-Physical Ecosystems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's distributed and pervasive computing addresses large-scale cyber-physical ecosystems, characterised by dense and large networks of devices capable of computation, communication and interaction with the environment and people. While most research focusses on treating these systems as "composites" (i.e., heterogeneous functional complexes), recent developments in fields such as self-organising systems and swarm robotics have opened up a complementary perspective: treating systems as "collectives" (i.e., uniform, collaborative, and self-organising groups of entities). This article explores the motivations, state of the art, and implications of this "collective computing paradigm" in software engineering, discusses its peculiar challenges, and outlines a path for future research, touching on aspects such as macroprogramming, collective intelligence, self-adaptive middleware, learning, synthesis, and experimentation of collective behaviour. </t>
+  </si>
+  <si>
+    <t>Morescient GAI for Software Engineering (Extended Version)</t>
+  </si>
+  <si>
+    <t>The ability of Generative AI (GAI) technology to automatically check, synthesize and modify software engineering artifacts promises to revolutionize all aspects of software engineering. Using GAI for software engineering tasks is consequently one of the most rapidly expanding fields of software engineering research, with over a hundred LLM-based code models having been published since 2021. However, the overwhelming majority of existing code models share a major weakness - they are exclusively trained on the syntactic facet of software, significantly lowering their trustworthiness in tasks dependent on software semantics. To address this problem, a new class of "Morescient" GAI is needed that is "aware" of (i.e., trained on) both the semantic and static facets of software. This, in turn, will require a new generation of software observation platforms capable of generating large quantities of execution observations in a structured and readily analyzable way. In this paper, we present a vision and roadmap for how such "Morescient" GAI models can be engineered, evolved and disseminated according to the principles of open science.</t>
+  </si>
+  <si>
+    <t>A Road-Map for Transferring Software Engineering methods for Model-Based Early V&amp;V of Behaviour to Systems Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In this paper we discuss the growing need for system behaviour to be validated and verified (V&amp;V'ed) early in model-based systems engineering. Several aspects push companies towards integration of techniques, methods, and processes that promote specific and general V&amp;V activities earlier to support more effective decision-making. As a result, there are incentives to introduce new technologies to remain competitive with the recently drastic changes in system complexity and heterogeneity. Performing V&amp;V early on in development is a means of reducing risk for later error detection while moving key activities earlier in a process. We present a summary of the literature on early V&amp;V and position existing challenges regarding potential solutions and future investigations. In particular, we reason that the software engineering community can act as a source for inspiration as many emerging technologies in the software domain are showing promise in the wider systems domain, and there already exist well formed methods for early V&amp;V of software behaviour in the software modelling community. We conclude the paper with a road-map for future research and development for both researchers and practitioners to further develop the concepts discussed in the paper. </t>
+  </si>
+  <si>
+    <t>Understanding and measuring software engineer behavior: What can we learn from the behavioral sciences?</t>
+  </si>
+  <si>
+    <t>This paper explores the intricate challenge of understanding and measuring software engineer behavior. More specifically, we revolve around a central question: How can we enhance our understanding of software engineer behavior? Grounded in the nuanced complexities addressed within Behavioral Software Engineering (BSE), we advocate for holistic methods that integrate quantitative measures, such as psychometric instruments, and qualitative data from diverse sources. Furthermore, we delve into the relevance of this challenge within national and international contexts, highlighting the increasing interest in understanding software engineer behavior. Real-world initiatives and academic endeavors are also examined to underscore the potential for advancing this research agenda and, consequently, refining software engineering practices based on behavioral aspects. Lastly, this paper addresses different ways to evaluate the progress of this challenge by leveraging methodological skills derived from behavioral sciences, ultimately contributing to a deeper understanding of software engineer behavior and software engineering practices.</t>
+  </si>
+  <si>
+    <t>Investigating the Online Recruitment and Selection Journey of Novice Software Engineers: Anti-patterns and Recommendations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The growing software development market has increased the demand for qualified professionals in Software Engineering (SE). To this end, companies must enhance their Recruitment and Selection (R&amp;S) processes to maintain high quality teams, including opening opportunities for beginners, such as trainees and interns. However, given the various judgments and sociotechnical factors involved, this complex process of R&amp;S poses a challenge for recent graduates seeking to enter the market. [Objective] This paper aims to identify a set of anti-patterns and recommendations for early career SE professionals concerning R&amp;S processes. [Method] Under an exploratory and qualitative methodological approach, we conducted six online Focus Groups with 18 recruiters with experience in R&amp;S in the software industry. [Results] After completing our qualitative analysis, we identified 12 anti-patterns and 31 actionable recommendations regarding the hiring process focused on entry level SE professionals. The identified anti-patterns encompass behavioral and technical dimensions innate to R&amp;S processes. [Conclusion] These findings provide a rich opportunity for reflection in the SE industry and offer valuable guidance for early-career candidates and organizations. From an academic perspective, this work also raises awareness of the intersection of Human Resources and SE, an area with considerable potential to be expanded in the context of cooperative and human aspects of SE</t>
+  </si>
+  <si>
+    <t>An Overview of Quantum Software Engineering in Latin America</t>
+  </si>
+  <si>
+    <t>Quantum computing represents a revolutionary computational paradigm with the potential to address challenges beyond classical computers' capabilities. The development of robust quantum software is indispensable to unlock the full potential of quantum computing. Like classical software, quantum software is expected to be complex and extensive, needing the establishment of a specialized field known as Quantum Software Engineering. Recognizing the regional focus on Latin America within this special issue, we have boarded on an in-depth inquiry encompassing a systematic mapping study of existing literature and a comprehensive survey of experts in the field. This rigorous research effort aims to illuminate the current landscape of Quantum Software Engineering initiatives undertaken by universities, research institutes, and companies across Latin America. This exhaustive study aims to provide information on the progress, challenges, and opportunities in Quantum Software Engineering in the Latin American context. By promoting a more in-depth understanding of cutting-edge developments in this burgeoning field, our research aims to serve as a potential stimulus to initiate pioneering initiatives and encourage collaborative efforts among Latin American researchers.</t>
+  </si>
+  <si>
+    <t>Unlocking Futures: A Natural Language Driven Career Prediction System for Computer Science and Software Engineering Students</t>
+  </si>
+  <si>
+    <t>A career is a crucial aspect for any person to fulfill their desires through hard work. During their studies, students cannot find the best career suggestions unless they receive meaningful guidance tailored to their skills. Therefore, we developed an AI-assisted model for early prediction to provide better career suggestions. Although the task is difficult, proper guidance can make it easier. Effective career guidance requires understanding a student's academic skills, interests, and skill-related activities. In this research, we collected essential information from Computer Science (CS) and Software Engineering (SWE) students to train a machine learning (ML) model that predicts career paths based on students' career-related information. To adequately train the models, we applied Natural Language Processing (NLP) techniques and completed dataset pre-processing. For comparative analysis, we utilized multiple classification ML algorithms and deep learning (DL) algorithms. This study contributes valuable insights to educational advising by providing specific career suggestions based on the unique features of CS and SWE students. Additionally, the research helps individual CS and SWE students find suitable jobs that match their skills, interests, and skill-related activities.</t>
+  </si>
+  <si>
+    <t>SWE-agent: Agent-Computer Interfaces Enable Automated Software Engineering</t>
+  </si>
+  <si>
+    <t>Language model (LM) agents are increasingly being used to automate complicated tasks in digital environments. Just as humans benefit from powerful software applications, such as integrated development environments, for complex tasks like software engineering, we posit that LM agents represent a new category of end users with their own needs and abilities, and would benefit from specially-built interfaces to the software they use. We investigate how interface design affects the performance of language model agents. As a result of this exploration, we introduce SWE-agent: a system that facilitates LM agents to autonomously use computers to solve software engineering tasks. SWE-agent's custom agent-computer interface (ACI) significantly enhances an agent's ability to create and edit code files, navigate entire repositories, and execute tests and other programs. We evaluate SWE-agent on SWE-bench and HumanEvalFix, achieving state-of-the-art performance on both with a pass@1 rate of 12.5% and 87.7%, respectively, far exceeding the previous state-of-the-art achieved with non-interactive LMs. Finally, we provide insight on how the design of the ACI can impact agents' behavior and performance.</t>
+  </si>
+  <si>
+    <t>Requirements are All You Need: The Final Frontier for End-User Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What if end users could own the software development lifecycle from conception to deployment using only requirements expressed in language, images, video or audio? We explore this idea, building on the capabilities that generative Artificial Intelligence brings to software generation and maintenance techniques. How could designing software in this way better serve end users? What are the implications of this process for the future of end-user software engineering and the software development lifecycle? We discuss the research needed to bridge the gap between where we are today and these imagined systems of the future. </t>
+  </si>
+  <si>
+    <t>Automated categorization of pre-trained models for software engineering: A case study with a Hugging Face dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software engineering (SE) activities have been revolutionized by the advent of pre-trained models (PTMs), defined as large machine learning (ML) models that can be fine-tuned to perform specific SE tasks. However, users with limited expertise may need help to select the appropriate model for their current task. To tackle the issue, the Hugging Face (HF) platform simplifies the use of PTMs by collecting, storing, and curating several models. Nevertheless, the platform currently lacks a comprehensive categorization of PTMs designed specifically for SE, i.e., the existing tags are more suited to generic ML categories. This paper introduces an approach to address this gap by enabling the automatic classification of PTMs for SE tasks. First, we utilize a public dump of HF to extract PTMs information, including model documentation and associated tags. Then, we employ a semi-automated method to identify SE tasks and their corresponding PTMs from existing literature. The approach involves creating an initial mapping between HF tags and specific SE tasks, using a similarity-based strategy to identify PTMs with relevant tags. The evaluation shows that model cards are informative enough to classify PTMs considering the pipeline tag. Moreover, we provide a mapping between SE tasks and stored PTMs by relying on model names.</t>
+  </si>
+  <si>
+    <t>From Human-to-Human to Human-to-Bot Conversations in Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software developers use natural language to interact not only with other humans, but increasingly also with chatbots. These interactions have different properties and flow differently based on what goal the developer wants to achieve and who they interact with. In this paper, we aim to understand the dynamics of conversations that occur during modern software development after the integration of AI and chatbots, enabling a deeper recognition of the advantages and disadvantages of including chatbot interactions in addition to human conversations in collaborative work. We compile existing conversation attributes with humans and NLU-based chatbots and adapt them to the context of software development. Then, we extend the comparison to include LLM-powered chatbots based on an observational study. We present similarities and differences between human-to-human and human-to-bot conversations, also distinguishing between NLU- and LLM-based chatbots. Furthermore, we discuss how understanding the differences among the conversation styles guides the developer on how to shape their expectations from a conversation and consequently support the communication within a software team. We conclude that the recent conversation styles that we observe with LLM-chatbots can not replace conversations with humans due to certain attributes regarding social aspects despite their ability to support productivity and decrease the developers' mental load. </t>
+  </si>
+  <si>
+    <t>A Vision on Open Science for the Evolution of Software Engineering Research and Practice</t>
+  </si>
+  <si>
+    <t>Open Science aims to foster openness and collaboration in research, leading to more significant scientific and social impact. However, practicing Open Science comes with several challenges and is currently not properly rewarded. In this paper, we share our vision for addressing those challenges through a conceptual framework that connects essential building blocks for a change in the Software Engineering community, both culturally and technically. The idea behind this framework is that Open Science is treated as a first-class requirement for better Software Engineering research, practice, recognition, and relevant social impact. There is a long road for us, as a community, to truly embrace and gain from the benefits of Open Science. Nevertheless, we shed light on the directions for promoting the necessary culture shift and empowering the Software Engineering community.</t>
+  </si>
+  <si>
+    <t>Preconceptual Modeling in Software Engineering: Metaphysics of Diagrammatic Representations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">According to many researchers, conceptual model (CM) development is a hard task, and system requirements are difficult to collect, causing many miscommunication problems. CMs require more than modeling ability alone - they first require an understanding of the targeted domain that the model attempts to represent. Accordingly, a preconceptual modeling (pre-CM) stage is intended to address ontological issues before typical CM development is initiated. It involves defining a portion of reality when entities and processes are differentiated and integrated as unified wholes. This pre-CM phase forms the focus of research in this paper. The purpose is not show how to model; rather, it is to demonstrate how to establish a metaphysical basis of the involved portion of reality. To demonstrate such a venture, we employ the so-called thinging machine (TM) modeling that has been proposed as a high-level CM. A TM model integrates staticity and dynamism grounded in a fundamental construct called a thimac (things/machine). It involves two modes of reality, existence (events) and subsistence (regions - roughly, specifications of things and processes). Currently, the dominant approach in CM has evolved to limit its scope of application to develop ontological categorization (types of things). In the TM approach, pre-CM metaphysics is viewed as a part and parcel of CM itself. The general research problem is how to map TM constructs to what is out there in the targeted domain. Discussions involve the nature of thimacs (things and processes) and subsistence and existence as they are superimposed over each other in reality. Specifically, we make two claims, (a) the perceptibility of regions as a phenomenon and (b) the distinctiveness of existence as a construct for events. The results contribute to further the understanding of TM modeling in addition to introducing some metaphysical insights. </t>
+  </si>
+  <si>
+    <t>Requirements Engineering for Research Software: A Vision</t>
+  </si>
+  <si>
+    <t>Modern science is relying on software more than ever. The behavior and outcomes of this software shape the scientific and public discourse on important topics like climate change, economic growth, or the spread of infections. Most researchers creating software for scientific purposes are not trained in Software Engineering. As a consequence, research software is often developed ad hoc without following stringent processes. With this paper, we want to characterize research software as a new application domain that needs attention from the Requirements Engineering community. We conducted an exploratory study based on 8 interviews with 12 researchers who develop software. We describe how researchers elicit, document, and analyze requirements for research software and what processes they follow. From this, we derive specific challenges and describe a vision of Requirements Engineering for research software.</t>
+  </si>
+  <si>
+    <t>Gamification in Software Engineering Education: a Tertiary Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As the significance of Software Engineering (SE) professionals continues to grow in the industry, the adoption of gamification techniques for training purposes has gained traction due to its potential to enhance class appeal through game-derived elements. This paper presents a tertiary study investigating the application of gamification in Software Engineering (SE) education. The study was conducted in response to recent systematic literature reviews and mappings on the topic. The findings reveal that the areas of SE most frequently gamified are Software Testing and Software Quality, with competition and cooperation being the most commonly utilized gamification elements. Additionally, the majority of studies focus on structural gamification, where game elements are employed to modify the learning environment without altering the content. The results demonstrate the potential of gamification to improve students' engagement and motivation throughout the SE learning process, while also impacting other aspects such as performance improvement, skill development, and fostering good SE practices. However, caution is advised as unplanned and incorrectly applied gamification measures may lead to significant declines in performance and motivation. </t>
+  </si>
+  <si>
+    <t>6G Software Engineering: A Systematic Mapping Study</t>
+  </si>
+  <si>
+    <t>6G will revolutionize the software world allowing faster cellular communications and a massive number of connected devices. 6G will enable a shift towards a continuous edge-to-cloud architecture. Current cloud solutions, where all the data is transferred and computed in the cloud, are not sustainable in such a large network of devices. Current technologies, including development methods, software architectures, and orchestration and offloading systems, still need to be prepared to cope with such requirements. In this paper, we conduct a Systematic Mapping Study to investigate the current research status of 6G Software Engineering. Results show that 18 research papers have been proposed in software process, software architecture, orchestration and offloading methods. Of these, software architecture and software-defined networks are respectively areas and topics that have received the most attention in 6G Software Engineering. In addition, the main types of results of these papers are methods, architectures, platforms, frameworks and algorithms. For the five tools/frameworks proposed, they are new and not currently studied by other researchers. The authors of these findings are ma</t>
+  </si>
+  <si>
+    <t>The Impact of Human Aspects on the Interactions Between Software Developers and End-Users in Software Engineering: A Systematic Literature Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context: Research on human aspects within the field of software engineering (SE) has been steadily gaining prominence in recent years. These human aspects have a significant impact on SE due to the inherently interactive and collaborative nature of the discipline. Objective: In this paper, we present a systematic literature review (SLR) on human aspects affecting developer-user interactions. The objective of this SLR is to plot the current landscape of primary studies by examining the human aspects that influence developer-user interactions, their implications, interrelationships, and how existing studies address these implications. Method: We conducted this SLR following the guidelines proposed by Kitchenham et al. We performed a comprehensive search in six digital databases, and an exhaustive backward and forward snowballing process. We selected 46 primary studies for data extraction. Results: We identified various human aspects affecting developer-user interactions in SE, assessed their interrelationships, identified their positive impacts and mitigation strategies for negative effects. We present specific recommendations derived from the identified research gaps. Conclusion: Our findings suggest the importance of leveraging positive effects and addressing negative effects in developer-user interactions through the implementation of effective mitigation strategies. These insights may benefit software practitioners for effective user interactions, and the recommendations proposed by this SLR may aid the research community in further human aspects related studies. </t>
+  </si>
+  <si>
+    <t>Breaking Barriers: Investigating the Sense of Belonging Among Women and Non-Binary Students in Software Engineering</t>
+  </si>
+  <si>
+    <t>Women in computing were among the first programmers in the early 20th century and were substantial contributors to the industry. Today, men dominate the software engineering industry. Research and data show that women are far less likely to pursue a career in this industry, and those that do are less likely than men to stay in it. Reasons for women and other underrepresented minorities to leave the industry are a lack of opportunities for growth and advancement, unfair treatment and workplace culture. This research explores how the potential to cultivate or uphold an industry unfavourable to women and non-binary individuals manifests in software engineering education at the university level. For this purpose, the study includes surveys and interviews. We use gender name perception as a survey instrument, and the results show small differences in perceptions of software engineering students based on their gender. Particularly, the survey respondents anchor the values of the male software engineer (Hans) to a variety of technical and non-technical skills, while the same description for a female software engineer (Hanna) is anchored mainly by her managerial skills. With interviews with women and non-binary students, we gain insight on the main barriers to their sense of ambient belonging. The collected data shows that some known barriers from the literature such as tokenism, and stereotype threat, do still exist. However, we find positive factors such as role models and encouragement that strengthen the sense of belonging among these students.</t>
+  </si>
+  <si>
+    <t>A Diagramming Technique for Teaching Students to Read Software Engineering Research Papers: an experience report</t>
+  </si>
+  <si>
+    <t>Reading scientific research papers is a skill that many students do not learn before entering PhD programs, but it is critical to their success. This paper describes our diagramming technique for teaching this skill, which helps them identify the structure and the scientific argument of the paper. This has made our students more effective readers.</t>
+  </si>
+  <si>
+    <t>From Quantum Mechanics to Quantum Software Engineering: A Historical Review</t>
+  </si>
+  <si>
+    <t>Victor Hugo's timeless observation, "Nothing is more powerful than an idea whose time has come", resonates today as Quantum Computing, once only a dream of a physicist, stands at the threshold of reality with the potential to revolutionise the world. To comprehend the surge of attention it commands today, one must delve into the motivations that birthed and nurtured Quantum Computing. While the past of Quantum Computing provides insights into the present, the future could unfold through the lens of Quantum Software Engineering. Quantum Software Engineering, guided by its principles and methodologies investigates the most effective ways to interact with Quantum Computers to unlock their true potential and usher in a new era of possibilities. To gain insight into the present landscape and anticipate the trajectory of Quantum Computing and Quantum Software Engineering, this paper embarks on a journey through their evolution and outlines potential directions for future research. By doing so, we aim to equip readers (ideally software engineers and computer scientists not necessarily with quantum expertise) with the insights necessary to navigate the ever-evolving landscape of Quantum Computing and anticipate the trajectories that lie ahead.</t>
+  </si>
+  <si>
+    <t>Reusing Deep Learning Models: Challenges and Directions in Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deep neural networks (DNNs) achieve state-of-the-art performance in many areas, including computer vision, system configuration, and question-answering. However, DNNs are expensive to develop, both in intellectual effort (e.g., devising new architectures) and computational costs (e.g., training). Reusing DNNs is a promising direction to amortize costs within a company and across the computing industry. As with any new technology, however, there are many challenges in reusing DNNs. These challenges include both missing technical capabilities and missing engineering practices. This vision paper describes challenges in current approaches to DNN re-use. We summarize studies of re-use failures across the spectrum of re-use techniques, including conceptual (e.g., reusing based on a research paper), adaptation (e.g., re-using by building on an existing implementation), and deployment (e.g., direct re-use on a new device). We outline possible advances that would improve each kind of re-use. </t>
+  </si>
+  <si>
+    <t>Who's actually being Studied? A Call for Population Analysis in Software Engineering Research</t>
+  </si>
+  <si>
+    <t>Population analysis is crucial for ensuring that empirical software engineering (ESE) research is representative and its findings are valid. Yet, there is a persistent gap between sampling processes and the holistic examination of populations, which this position paper addresses. We explore the challenges ranging from analysing populations of individual software engineers to organizations and projects. We discuss the interplay between generalizability and transferability and advocate for appropriate population frames. We also present a compelling case for improved population analysis aiming to enhance the empirical rigor and external validity of ESE research.</t>
+  </si>
+  <si>
+    <t>Beyond Code Generation: An Observational Study of ChatGPT Usage in Software Engineering Practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Models (LLMs) are frequently discussed in academia and the general public as support tools for virtually any use case that relies on the production of text, including software engineering. Currently there is much debate, but little empirical evidence, regarding the practical usefulness of LLM-based tools such as ChatGPT for engineers in industry. We conduct an observational study of 24 professional software engineers who have been using ChatGPT over a period of one week in their jobs, and qualitatively analyse their dialogues with the chatbot as well as their overall experience (as captured by an exit survey). We find that, rather than expecting ChatGPT to generate ready-to-use software artifacts (e.g., code), practitioners more often use ChatGPT to receive guidance on how to solve their tasks or learn about a topic in more abstract terms. We also propose a theoretical framework for how (i) purpose of the interaction, (ii) internal factors (e.g., the user's personality), and (iii) external factors (e.g., company policy) together shape the experience (in terms of perceived usefulness and trust). We envision that our framework can be used by future research to further the academic discussion on LLM usage by software engineering practitioners, and to serve as a reference point for the design of future empirical LLM research in this domain.</t>
+  </si>
+  <si>
+    <t>Object-Oriented Architecture: A Software Engineering-Inspired Shape Grammar for Durands Plates</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Addressing the challenge of modular architectural design, this study presents a novel approach through the implementation of a shape grammar system using functional and object-oriented programming principles from computer science. The focus lies on the modular generation of plates in the style of French Neoclassical architect Jean-Nicolas-Louis Durand, known for his modular rule-based method to architecture, demonstrating the system's capacity to articulate intricate architectural forms systematically. By leveraging computer programming principles, the proposed methodology allows for the creation of diverse designs while adhering to the inherent logic of Durand's original plates. The integration of Shape Machine allows a flexible framework for architects and designers, enabling the generation of complex structures in a modular fashion in existing CAD software. This research contributes to the exploration of computational tools in architectural design, offering a versatile solution for the synthesis of historically significant architectural elements.</t>
+  </si>
+  <si>
+    <t>Rethinking Software Engineering in the Foundation Model Era: From Task-Driven AI Copilots to Goal-Driven AI Pair Programmers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The advent of Foundation Models (FMs) and AI-powered copilots has transformed the landscape of software development, offering unprecedented code completion capabilities and enhancing developer productivity. However, the current task-driven nature of these copilots falls short in addressing the broader goals and complexities inherent in software engineering (SE). In this paper, we propose a paradigm shift towards goal-driven AI-powered pair programmers that collaborate with human developers in a more holistic and context-aware manner. We envision AI pair programmers that are goal-driven, human partners, SE-aware, and self-learning. These AI partners engage in iterative, conversation-driven development processes, aligning closely with human goals and facilitating informed decision-making. We discuss the desired attributes of such AI pair programmers and outline key challenges that must be addressed to realize this vision. Ultimately, our work represents a shift from AI-augmented SE to AI-transformed SE by replacing code completion with a collaborative partnership between humans and AI that enhances both productivity and software quality.</t>
+  </si>
+  <si>
+    <t>Software Engineering Methods For AI-Driven Deductive Legal Reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The recent proliferation of generative artificial intelligence (AI) technologies such as pre-trained large language models (LLMs) has opened up new frontiers in computational law. An exciting area of development is the use of AI to automate the deductive rule-based reasoning inherent in statutory and contract law. This paper argues that such automated deductive legal reasoning can now be viewed from the lens of software engineering, treating LLMs as interpreters of natural-language programs with natural-language inputs. We show how it is possible to apply principled software engineering techniques to enhance AI-driven legal reasoning of complex statutes and to unlock new applications in automated meta-reasoning such as mutation-guided example generation and metamorphic property-based testing. </t>
+  </si>
+  <si>
+    <t>Research Artifacts in Software Engineering Publications: Status and Trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The Software Engineering (SE) community has been embracing the open science policy and encouraging researchers to disclose artifacts in their publications. However, the status and trends of artifact practice and quality remain unclear, lacking insights on further improvement. In this paper, we present an empirical study to characterize the research artifacts in SE publications. Specifically, we manually collect 1,487 artifacts from all 2,196 papers published in top-tier SE conferences (ASE, FSE, ICSE, and ISSTA) from 2017 to 2022. We investigate the common practices (e.g., URL location and format, storage websites), maintenance activities (e.g., last update time and URL validity), popularity (e.g., the number of stars on GitHub and characteristics), and quality (e.g., documentation and code smell) of these artifacts. Based on our analysis, we reveal a rise in publications providing artifacts. The usage of Zenodo for sharing artifacts has significantly increased. However, artifacts stored in GitHub tend to receive few stars, indicating a limited influence on real-world SE applications. We summarize the results and provide suggestions to different stakeholders in conjunction with current guidelines.</t>
+  </si>
+  <si>
+    <t>Quantum Software Engineering: Roadmap and Challenges Ahead</t>
+  </si>
+  <si>
+    <t>As quantum computers advance, the complexity of the software they can execute increases as well. To ensure this software is efficient, maintainable, reusable, and cost-effective -key qualities of any industry-grade software-mature software engineering practices must be applied throughout its design, development, and operation. However, the significant differences between classical and quantum software make it challenging to directly apply classical software engineering methods to quantum systems. This challenge has led to the emergence of Quantum Software Engineering as a distinct field within the broader software engineering landscape. In this work, a group of active researchers analyse in depth the current state of quantum software engineering research. From this analysis, the key areas of quantum software engineering are identified and explored in order to determine the most relevant open challenges that should be addressed in the next years. These challenges help identify necessary breakthroughs and future research directions for advancing Quantum Software Engineering.</t>
+  </si>
+  <si>
+    <t>Guiding Principles for Using Mixed Methods Research in Software Engineering</t>
+  </si>
+  <si>
+    <t>Mixed methods research is often used in software engineering, but researchers outside of the social or human sciences often lack experience when using these designs. This paper provides guiding principles and advice on how to design mixed method research, and to encourage the intentional, rigorous, and innovative application of mixed methods in software engineering. It also presents key properties of core mixed method research designs. Through a number of fictitious but recognizable software engineering research scenarios, we showcase how to choose suitable designs and consider the inevitable trade-offs any design choice leads to. We describe several antipatterns that illustrate what to avoid in mixed method research, and when mixed method research should be considered over other approaches.</t>
+  </si>
+  <si>
+    <t>LLM-Based Multi-Agent Systems for Software Engineering: Literature Review, Vision and the Road Ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrating Large Language Models (LLMs) into autonomous agents marks a significant shift in the research landscape by offering cognitive abilities that are competitive with human planning and reasoning. This paper explores the transformative potential of integrating Large Language Models into Multi-Agent (LMA) systems for addressing complex challenges in software engineering (SE). By leveraging the collaborative and specialized abilities of multiple agents, LMA systems enable autonomous problem-solving, improve robustness, and provide scalable solutions for managing the complexity of real-world software projects. In this paper, we conduct a systematic review of recent primary studies to map the current landscape of LMA applications across various stages of the software development lifecycle (SDLC). To illustrate current capabilities and limitations, we perform two case studies to demonstrate the effectiveness of state-of-the-art LMA frameworks. Additionally, we identify critical research gaps and propose a comprehensive research agenda focused on enhancing individual agent capabilities and optimizing agent synergy. Our work outlines a forward-looking vision for developing fully autonomous, scalable, and trustworthy LMA systems, laying the foundation for the evolution of Software Engineering 2.0. </t>
+  </si>
+  <si>
+    <t>Efficient and Green Large Language Models for Software Engineering: Literature Review, Vision, and the Road Ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Models (LLMs) have recently shown remarkable capabilities in various software engineering tasks, spurring the rapid growth of the Large Language Models for Software Engineering (LLM4SE) area. However, limited attention has been paid to developing efficient LLM4SE techniques that demand minimal computational cost, time, and memory resources, as well as green LLM4SE solutions that reduce energy consumption, water usage, and carbon emissions. This paper aims to redirect the focus of the research community towards the efficiency and greenness of LLM4SE, while also sharing potential research directions to achieve this goal. It commences with a brief overview of the significance of LLM4SE and highlights the need for efficient and green LLM4SE solutions. Subsequently, the paper presents a vision for a future where efficient and green LLM4SE revolutionizes the LLM-based software engineering tool landscape, benefiting various stakeholders, including industry, individual practitioners, and society. The paper then delineates a roadmap for future research, outlining specific research paths and potential solutions for the research community to pursue. While not intended to be a definitive guide, the paper aims to inspire further progress, with the ultimate goal of establishing efficient and green LLM4SE as a central element in the future of software engineering.</t>
+  </si>
+  <si>
+    <t>AI-Tutoring in Software Engineering Education</t>
+  </si>
+  <si>
+    <t>With the rapid advancement of artificial intelligence (AI) in various domains, the education sector is set for transformation. The potential of AI-driven tools in enhancing the learning experience, especially in programming, is immense. However, the scientific evaluation of Large Language Models (LLMs) used in Automated Programming Assessment Systems (APASs) as an AI-Tutor remains largely unexplored. Therefore, there is a need to understand how students interact with such AI-Tutors and to analyze their experiences. In this paper, we conducted an exploratory case study by integrating the GPT-3.5-Turbo model as an AI-Tutor within the APAS Artemis. Through a combination of empirical data collection and an exploratory survey, we identified different user types based on their interaction patterns with the AI-Tutor. Additionally, the findings highlight advantages, such as timely feedback and scalability. However, challenges like generic responses and students' concerns about a learning progress inhibition when using the AI-Tutor were also evident. This research adds to the discourse on AI's role in education.</t>
+  </si>
+  <si>
+    <t>Seeking Enlightenment: Incorporating Evidence-Based Practice Techniques in a Research Software Engineering Team</t>
+  </si>
+  <si>
+    <t>Evidence-based practice (EBP) in software engineering aims to improve decision-making in software development by complementing practitioners' professional judgment with high-quality evidence from research. We believe the use of EBP techniques may be helpful for research software engineers (RSEs) in their work to bring software engineering best practices to scientific software development. In this study, we present an experience report on the use of a particular EBP technique, rapid reviews, within an RSE team at Sandia National Laboratories, and present practical recommendations for how to address barriers to EBP adoption within the RSE community.</t>
+  </si>
+  <si>
+    <t>Looking back and forward: A retrospective and future directions on Software Engineering for systems-of-systems</t>
+  </si>
+  <si>
+    <t>Modern systems are increasingly connected and more integrated with other existing systems, giving rise to \textit{systems-of-systems} (SoS). An SoS consists of a set of independent, heterogeneous systems that interact to provide new functionalities and accomplish global missions through emergent behavior manifested at runtime. The distinctive characteristics of SoS, when contrasted to traditional systems, pose significant research challenges within Software Engineering. These challenges motivate the need for a paradigm shift and the exploration of novel approaches for designing, developing, deploying, and evolving these systems. The \textit{International Workshop on Software Engineering for Systems-of-Systems} (SESoS) series started in 2013 to fill a gap in scientific forums addressing SoS from the Software Engineering perspective, becoming the first venue for this purpose. This article presents a study aimed at outlining the evolution and future trajectory of Software Engineering for SoS based on the examination of 57 papers spanning the 11 editions of the SESoS workshop (2013-2023). The study combined scoping review and scientometric analysis methods to categorize and analyze the research contributions concerning temporal and geographic distribution, topics of interest, research methodologies employed, application domains, and research impact. Based on such a comprehensive overview, this article discusses current and future directions in Software Engineering for SoS.</t>
+  </si>
+  <si>
+    <t>Advancing Quantum Software Engineering: A Vision of Hybrid Full-Stack Iterative Model</t>
+  </si>
+  <si>
+    <t>This paper introduces a vision for Quantum Software Development lifecycle, proposing a hybrid full-stack iterative model that integrates quantum and classical computing. Addressing the current challenges in Quantum Computing (QC) such as the need for integrating diverse programming languages and managing the complexities of quantum-classical systems, this model is rooted in the principles of DevOps and continuous software engineering. It presents a comprehensive lifecycle for quantum software development, encompassing quantum-agnostic coding, testing, deployment, cloud computing services, orchestration, translation, execution, and interpretation phases. Each phase is designed to accommodate the unique demands of QC, enabling traditional software developers to engage with QC environments without needing in-depth QC expertise. The paper presents a detailed implementation roadmap, utilizing a range of existing tools and frameworks, thereby making quantum software development more accessible and efficient. The proposed model not only addresses current challenges in quantum software development but also makes a substantial contribution to the field of Quantum Software Engineering (QSE). By proposing a structured and accessible model, it sets the stage for further advancements and research in QSE, enhancing its practicality and relevance in a wide range of applications.</t>
+  </si>
+  <si>
+    <t>Lessons from a Pioneering Software Engineering Environment: Design Principles of Software through Pictures</t>
+  </si>
+  <si>
+    <t>This paper describes the historical background that led to the development of the innovative Software through Pictures multi-user development environment, and the principles for its integration with other software products to create a software engineering environment covering multiple tasks in the software development lifecycle.</t>
+  </si>
+  <si>
+    <t>Engineering Formality and Software Risk in Debian Python Packages</t>
+  </si>
+  <si>
+    <t>While free/libre and open source software (FLOSS) is critical to global computing infrastructure, the maintenance of widely-adopted FLOSS packages is dependent on volunteer developers who select their own tasks. Risk of failure due to the misalignment of engineering supply and demand -- known as underproduction -- has led to code base decay and subsequent cybersecurity incidents such as the Heartbleed and Log4Shell vulnerabilities. FLOSS projects are self-organizing but can often expand into larger, more formal efforts. Although some prior work suggests that becoming a more formal organization decreases project risk, other work suggests that formalization may increase the likelihood of project abandonment. We evaluate the relationship between underproduction and formality, focusing on formal structure, developer responsibility, and work process management. We analyze 182 packages written in Python and made available via the Debian GNU/Linux distribution. We find that although more formal structures are associated with higher risk of underproduction, more elevated developer responsibility is associated with less underproduction, and the relationship between formal work process management and underproduction is not statistically significant. Our analysis suggests that a FLOSS organization's transformation into a more formal structure may face unintended consequences which must be carefully managed.</t>
+  </si>
+  <si>
+    <t>Generative Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rapid development of deep learning techniques, improved computational power, and the availability of vast training data have led to significant advancements in pre-trained models and large language models (LLMs). Pre-trained models based on architectures such as BERT and Transformer, as well as LLMs like ChatGPT, have demonstrated remarkable language capabilities and found applications in Software engineering. Software engineering tasks can be divided into many categories, among which generative tasks are the most concern by researchers, where pre-trained models and LLMs possess powerful language representation and contextual awareness capabilities, enabling them to leverage diverse training data and adapt to generative tasks through fine-tuning, transfer learning, and prompt engineering. These advantages make them effective tools in generative tasks and have demonstrated excellent performance. In this paper, we present a comprehensive literature review of generative tasks in SE using pre-trained models and LLMs. We accurately categorize SE generative tasks based on software engineering methodologies and summarize the advanced pre-trained models and LLMs involved, as well as the datasets and evaluation metrics used. Additionally, we identify key strengths, weaknesses, and gaps in existing approaches, and propose potential research directions. This review aims to provide researchers and practitioners with an in-depth analysis and guidance on the application of pre-trained models and LLMs in generative tasks within SE. </t>
+  </si>
+  <si>
+    <t>Understanding Fairness in Software Engineering: Insights from Stack Exchange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software practitioners discuss problems at work with peers, in-person and online. These discussions can be technical (e.g., how to fix a bug?) and social (e.g., how to assign work fairly?). While there is a growing body of knowledge exploring fairness problems and solutions in the human and social factors of software engineering, most focus has been on specific problems. This study provides fairness discussions by software practitioners on Stack Exchange sites. We present an exploratory study presenting the fairness experience of software practitioners and fairness expectations in software teams. We also want to identify the fairness aspects software practitioners talk about the most. For example, do they care more about fairness in income or how they are treated in the workplace? Our investigation of fairness discussions on eight Stack Exchange sites resulted in a list of 136 posts (28 questions and 108 answers) manually curated from 4,178 candidate posts. The study reveals that the majority of fairness discussions (24 posts) revolve around the topic of income suggesting that many software practitioners are highly interested in matters related to their pay and how it is fairly distributed. Further, we noted that while not discussed as often, discussions on fairness in recruitment tend to receive the highest number of views and scores. Interestingly, the study shows that unfairness experiences extend beyond the protected attributes. In this study, only 25 out of 136 posts mention protected attributes, with gender mainly being discussed. </t>
+  </si>
+  <si>
+    <t>DevPhish: Exploring Social Engineering in Software Supply Chain Attacks on Developers</t>
+  </si>
+  <si>
+    <t>The Software Supply Chain (SSC) has captured considerable attention from attackers seeking to infiltrate systems and undermine organizations. There is evidence indicating that adversaries utilize Social Engineering (SocE) techniques specifically aimed at software developers. That is, they interact with developers at critical steps in the Software Development Life Cycle (SDLC), such as accessing Github repositories, incorporating code dependencies, and obtaining approval for Pull Requests (PR) to introduce malicious code. This paper aims to comprehensively explore the existing and emerging SocE tactics employed by adversaries to trick Software Engineers (SWEs) into delivering malicious software. By analyzing a diverse range of resources, which encompass established academic literature and real-world incidents, the paper systematically presents an overview of these manipulative strategies within the realm of the SSC. Such insights prove highly beneficial for threat modeling and security gap analysis.</t>
+  </si>
+  <si>
+    <t>The Second Round: Diverse Paths Towards Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the extant literature, there has been discussion on the drivers and motivations of minorities to enter the software industry. For example, universities have invested in more diverse imagery for years to attract a more diverse pool of students. However, in our research, we consider whether we understand why students choose their current major and how they did in the beginning decided to apply to study software engineering. We were also interested in learning if there could be some signs that would help us in marketing to get more women into tech. We approached the topic via an online survey (N = 78) sent to the university students of software engineering in Finland. Our results show that, on average, women apply later to software engineering studies than men, with statistically significant differences between genders. Additionally, we found that marketing actions have different impacts based on gender: personal guidance in live events or platforms is most influential for women, whereas teachers and social media have a more significant impact on men. The results also indicate two main paths into the field: the traditional linear educational pathway and the adult career change pathway, each significantly varying by gender </t>
+  </si>
+  <si>
+    <t>Rethinking Software Engineering in the Foundation Model Era: A Curated Catalogue of Challenges in the Development of Trustworthy Fmware</t>
+  </si>
+  <si>
+    <t>Foundation models (FMs), such as Large Language Models (LLMs), have revolutionized software development by enabling new use cases and business models. We refer to software built using FMs as FMware. The unique properties of FMware (e.g., prompts, agents, and the need for orchestration), coupled with the intrinsic limitations of FMs (e.g., hallucination) lead to a completely new set of software engineering challenges. Based on our industrial experience, we identified 10 key SE4FMware challenges that have caused enterprise FMware development to be unproductive, costly, and risky. In this paper, we discuss these challenges in detail and state the path for innovation that we envision. Next, we present FMArts, which is our long-term effort towards creating a cradle-to-grave platform for the engineering of trustworthy FMware. Finally, we (i) show how the unique properties of FMArts enabled us to design and develop a complex FMware for a large customer in a timely manner and (ii) discuss the lessons that we learned in doing so. We hope that the disclosure of the aforementioned challenges and our associated efforts to tackle them will not only raise awareness but also promote deeper and further discussions, knowledge sharing, and innovative solutions across the software engineering discipline</t>
+  </si>
+  <si>
+    <t>Language-Driven Engineering An Interdisciplinary Software Development Paradigm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> We illustrate how purpose-specific, graphical modeling enables application experts with different levels of expertise to collaboratively design and then produce complex applications using their individual, purpose-specific modeling language. Our illustration includes seven graphical Integrated Modeling Environments (IMEs) that support full code generation, as well as four browser-based applications that were modeled and then fully automatically generated and produced using DIME, our most complex graphical IME. While the seven IMEs were chosen to illustrate the types of languages we support with our Language-Driven Engineering (LDE) approach, the four DIME products were chosen to give an impression of the power of our LDE-generated IMEs. In fact, Equinocs, Springer Nature's future editorial system for proceedings, is also being fully automatically generated and then deployed at their Dordrecht site using a deployment pipeline generated with Rig, one of the IMEs presented. Our technology is open source and the products presented are currently in use.</t>
+  </si>
+  <si>
+    <t>Apples, Oranges, and Software Engineering: Study Selection Challenges for Secondary Research on Latent Variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Software engineering (SE) is full of abstract concepts that are crucial for both researchers and practitioners, such as programming experience, team productivity, code comprehension, and system security. Secondary studies aimed at summarizing research on the influences and consequences of such concepts would therefore be of great value. However, the inability to measure abstract concepts directly poses a challenge for secondary studies: primary studies in SE can operationalize such concepts in many ways. Standardized measurement instruments are rarely available, and even if they are, many researchers do not use them or do not even provide a definition for the studied concept. SE researchers conducting secondary studies therefore have to decide a) which primary studies intended to measure the same construct, and b) how to compare and aggregate vastly different measurements for the same construct. In this experience report, we discuss the challenge of study selection in SE secondary research on latent variables. We report on two instances where we found it particularly challenging to decide which primary studies should be included for comparison and synthesis, so as not to end up comparing apples with oranges. Our report aims to spark a conversation about developing strategies to address this issue systematically and pave the way for more efficient and rigorous secondary studies in software engineering.</t>
+  </si>
+  <si>
+    <t>Insights Towards Better Case Study Reporting in Software Engineering</t>
+  </si>
+  <si>
+    <t>Case studies are a popular and noteworthy type of research study in software engineering, offering significant potential to impact industry practices by investigating phenomena in their natural contexts. This potential to reach a broad audience beyond the academic community is often undermined by deficiencies in reporting, particularly in the context description, study classification, generalizability, and the handling of validity threats. This paper presents a reflective analysis aiming to share insights that can enhance the quality and impact of case study reporting. We emphasize the need to follow established guidelines, accurate classification, and detailed context descriptions in case studies. Additionally, particular focus is placed on articulating generalizable findings and thoroughly discussing generalizability threats. We aim to encourage researchers to adopt more rigorous and communicative strategies, ensuring that case studies are methodologically sound, resonate with, and apply to software engineering practitioners and the broader academic community. The reflections and recommendations offered in this paper aim to ensure that insights from case studies are transparent, understandable, and tailored to meet the needs of both academic researchers and industry practitioners. In doing so, we seek to enhance the real-world applicability of academic research, bridging the gap between theoretical research and practical implementation in industry.</t>
+  </si>
+  <si>
+    <t>Content and structure of laboratory packages for software engineering experiments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experiment replications play a central role in the scientific method. Although software engineering experimentation has matured a great deal, the number of experiment replications is still relatively small. Software engineering experiments are composed of complex concepts, procedures and artefacts. Laboratory packages are a means of transfer-ring knowledge among researchers to facilitate experiment replications. Objective: This paper investigates the experiment replication process to find out what information is needed to successfully replicate an experiment. Our objective is to propose the content and structure of laboratory packages for software engineering experiments. Method: We evaluated seven replications of three different families of experiments. Each replication had a different experimenter who was, at the time, unfamiliar with the experi-ment. During the first iterations of the study, we identified experimental incidents and then proposed a laboratory package structure that addressed these incidents, including docu-ment usability improvements. We used the later iterations to validate and generalize the laboratory package structure for use in all software engineering experiments. We aimed to solve a specific problem, while at the same time looking at how to contribute to the body of knowledge on laboratory packages. Results: We generated a laboratory package for three different experiments. These packages eased the replication of the respective experiments. The evaluation that we conducted shows that the laboratory package proposal is acceptable and reduces the effort currently required to replicate experiments in software engineering. Conclusion: We think that the content and structure that we propose for laboratory pack-ages can be useful for other software engineering experiments. </t>
+  </si>
+  <si>
+    <t>Can participation in a hackathon impact the motivation of software engineering students? A preliminary case study analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hackathons are increasingly gaining prominence in Software Engineering (SE) education, lauded for their ability to elevate students' skill sets. [Objective] This paper investigates whether hackathons can impact the motivation of SE students. [Method] We conducted an evaluative case study assessing students' motivations before and after a hackathon, combining quantitative analysis using the Academic Motivation Scale (AMS) and qualitative coding of open-ended responses. [Results] Pre-hackathon findings reveal a diverse range of motivations with an overall acceptance, while post-hackathon responses highlight no statistically significant shift in participants' perceptions. Qualitative findings uncovered themes related to networking, team dynamics, and skill development. From a practical perspective, our findings highlight the potential of hackathons to impact participants' motivation. [Conclusion] While our study enhances the comprehension of hackathons as a motivational tool, it also underscores the need for further exploration of psychometric dimensions in SE educational research. </t>
+  </si>
+  <si>
+    <t>On the Interaction between Software Engineers and Data Scientists when building Machine Learning-Enabled Systems</t>
+  </si>
+  <si>
+    <t>In recent years, Machine Learning (ML) components have been increasingly integrated into the core systems of organizations. Engineering such systems presents various challenges from both a theoretical and practical perspective. One of the key challenges is the effective interaction between actors with different backgrounds who need to work closely together, such as software engineers and data scientists. This paper presents an exploratory case study to understand the current interaction and collaboration dynamics between these roles in ML projects. We conducted semi-structured interviews with four practitioners with experience in software engineering and data science of a large ML-enabled system project and analyzed the data using reflexive thematic analysis. Our findings reveal several challenges that can hinder collaboration between software engineers and data scientists, including differences in technical expertise, unclear definitions of each role's duties, and the lack of documents that support the specification of the ML-enabled system. We also indicate potential solutions to address these challenges, such as fostering a collaborative culture, encouraging team communication, and producing concise system documentation. This study contributes to understanding the complex dynamics between software engineers and data scientists in ML projects and provides insights for improving collaboration and communication in this context. We encourage future studies investigating this interaction in other projects.</t>
+  </si>
+  <si>
+    <t>Assured LLM-Based Software Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In this paper we address the following question: How can we use Large Language Models (LLMs) to improve code independently of a human, while ensuring that the improved code - does not regress the properties of the original code? - improves the original in a verifiable and measurable way? To address this question, we advocate Assured LLM-Based Software Engineering; a generate-and-test approach, inspired by Genetic Improvement. Assured LLMSE applies a series of semantic filters that discard code that fails to meet these twin guarantees. This overcomes the potential problem of LLM's propensity to hallucinate. It allows us to generate code using LLMs, independently of any human. The human plays the role only of final code reviewer, as they would do with code generated by other human engineers. This paper is an outline of the content of the keynote by Mark Harman at the International Workshop on Interpretability, Robustness, and Benchmarking in Neural Software Engineering, Monday 15th April 2024, Lisbon, Portugal.</t>
+  </si>
+  <si>
+    <t>Information Systems and Software Engineering: The Case for Convergence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Information Systems (IS) and Software Engineering (SE) fields share a remarkable number of similarities in their historical evolution to date. These similarities are briefly outlined below. An analysis of 10 years (2001-2010) of publications in the primary journals in both fields also reveals a good deal of overlap in research topics. Given the challenges faced by both as young disciplines, there is potentially much to gain from a closer interaction between both fields than has traditionally been the case. This article seeks to encourage such interaction, and illustrates how this might usefully occur in the area of design. It concludes by proposing a number of practical initiatives that could stimulate and facilitate interaction between the IS and SE fields </t>
+  </si>
+  <si>
+    <t>Understanding the Building Blocks of Accountability in Software Engineering</t>
+  </si>
+  <si>
+    <t>In the social and organizational sciences, accountability has been linked to the efficient operation of organizations. However, it has received limited attention in software engineering (SE) research, in spite of its central role in the most popular software development methods (e.g., Scrum). In this article, we explore the mechanisms of accountability in SE environments. We investigate the factors that foster software engineers' individual accountability within their teams through an interview study with 12 people. Our findings recognize two primary forms of accountability shaping software engineers individual senses of accountability: institutionalized and grassroots. While the former is directed by formal processes and mechanisms, like performance reviews, grassroots accountability arises organically within teams, driven by factors such as peers' expectations and intrinsic motivation. This organic form cultivates a shared sense of collective responsibility, emanating from shared team standards and individual engineers' inner commitment to their personal, professional values, and self-set standards. While institutionalized accountability relies on traditional "carrot and stick" approaches, such as financial incentives or denial of promotions, grassroots accountability operates on reciprocity with peers and intrinsic motivations, like maintaining one's reputation in the team.</t>
+  </si>
+  <si>
+    <t>Online research platforms, such as Prolific, offer rapid access to diverse participant pools but also pose unique challenges in participant qualification and skill verification. Previous studies reported mixed outcomes and challenges in leveraging online platforms for the recruitment of qualified software engineers. Drawing from our experience in conducting three different studies using Prolific, we propose best practices for recruiting and screening participants to enhance the quality and relevance of both qualitative and quantitative software engineering (SE) research samples. We propose refined best practices for recruitment in SE research on Prolific. (1) Iterative and controlled prescreening, enabling focused and manageable assessment of submissions (2) task-oriented and targeted questions that assess technical skills, knowledge of basic SE concepts, and professional engagement. (3) AI detection to verify the authenticity of free-text responses. (4) Qualitative and manual assessment of responses, ensuring authenticity and relevance in participant answers (5) Additional layers of prescreening are necessary when necessary to collect data relevant to the topic of the study. (6) Fair or generous compensation post-qualification to incentivize genuine participation. By sharing our experiences and lessons learned, we contribute to the development of effective and rigorous methods for SE empirical research. particularly the ongoing effort to establish guidelines to ensure reliable data collection. These practices have the potential to transferability to other participant recruitment platforms.</t>
+  </si>
+  <si>
+    <t>An Architecture for Software Engineering Gamification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamification has been applied in software engineering to improve quality and results by increasing people's motivation and engagement. A systematic mapping has identified research gaps in the field, one of them being the difficulty of creating an integrated gamified environment comprising all the tools of an organization, since most existing gamified tools are custom developments or prototypes. In this paper, we propose a gamification software architecture that allows us to transform the work environment of a software organization into an integrated gamified environment, i.e., the organization can maintain its tools, and the rewards obtained by the users for their actions in different tools will mount up. We developed a gamification engine based on our proposal, and we carried out a case study in which we applied it in a real software development company. The case study shows that the gamification engine has allowed the company to create a gamified workplace by integrating custom developed tools and off-the-shelf tools such as Redmine, TestLink, or JUnit, with the gamification engine. Two main advantages can be highlighted: (i) our solution allows the organization to maintain its current tools, and (ii) the rewards for actions in any tool accumulate in a centralized gamified environment. </t>
+  </si>
+  <si>
+    <t>An Empirical Study on Usage and Perceptions of LLMs in a Software Engineering Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Models (LLMs) represent a leap in artificial intelligence, excelling in tasks using human language(s). Although the main focus of general-purpose LLMs is not code generation, they have shown promising results in the domain. However, the usefulness of LLMs in an academic software engineering project has not been fully explored yet. In this study, we explore the usefulness of LLMs for 214 students working in teams consisting of up to six members. Notably, in the academic course through which this study is conducted, students were encouraged to integrate LLMs into their development tool-chain, in contrast to most other academic courses that explicitly prohibit the use of LLMs. In this paper, we analyze the AI-generated code, prompts used for code generation, and the human intervention levels to integrate the code into the code base. We also conduct a perception study to gain insights into the perceived usefulness, influencing factors, and future outlook of LLM from a computer science student's perspective. Our findings suggest that LLMs can play a crucial role in the early stages of software development, especially in generating foundational code structures, and helping with syntax and error debugging. These insights provide us with a framework on how to effectively utilize LLMs as a tool to enhance the productivity of software engineering students, and highlight the necessity of shifting the educational focus toward preparing students for successful human-AI collaboration.</t>
+  </si>
+  <si>
+    <t>A Systematic Literature Review on Explainability for Machine/Deep Learning-based Software Engineering Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The remarkable achievements of Artificial Intelligence (AI) algorithms, particularly in Machine Learning (ML) and Deep Learning (DL), have fueled their extensive deployment across multiple sectors, including Software Engineering (SE). However, due to their black-box nature, these promising AI-driven SE models are still far from being deployed in practice. This lack of explainability poses unwanted risks for their applications in critical tasks, such as vulnerability detection, where decision-making transparency is of paramount importance. This paper endeavors to elucidate this interdisciplinary domain by presenting a systematic literature review of approaches that aim to improve the explainability of AI models within the context of SE. The review canvasses work appearing in the most prominent SE &amp; AI conferences and journals, and spans 108 papers across 23 unique SE tasks. Based on three key Research Questions (RQs), we aim to (1) summarize the SE tasks where XAI techniques have shown success to date; (2) classify and analyze different XAI techniques; and (3) investigate existing evaluation approaches. Based on our findings, we identified a set of challenges remaining to be addressed in existing studies, together with a set of guidelines highlighting potential opportunities we deemed appropriate and important for future work. </t>
+  </si>
+  <si>
+    <t>What Makes a Great Software Quality Assurance Engineer?</t>
+  </si>
+  <si>
+    <t>Software Quality Assurance (SQA) Engineers are responsible for assessing a product during every phase of the software development process to ensure that the outcomes of each phase and the final product possess the desired qualities. In general, a great SQA engineer needs to have a different set of abilities from development engineers to effectively oversee the entire product development process from beginning to end. Recent empirical studies identified important attributes of software engineers and managers, but the quality assurance role is overlooked. As software quality aspects have become more of a priority in the life cycle of software development, employers seek professionals that best suit the company's objectives and new graduates desire to make a valuable contribution through their job as an SQA engineer, but what makes them great? We addressed this knowledge gap by conducting 25 semi-structured interviews and 363 survey respondents with software quality assurance engineers from different companies around the world. We use the data collected from these activities to derive a comprehensive set of attributes that are considered important. As a result of the interviews, twenty-five attributes were identified and grouped into five main categories: personal, social, technical, management, and decision-making attributes. Through a rating survey, we confirmed that the distinguishing characteristics of great SQA engineers are curiosity, the ability to communicate effectively, and critical thinking skills. This work will guide further studies with SQA practitioners, by considering contextual factors and providing some implications for research and practice.</t>
+  </si>
+  <si>
+    <t>Software Engineering for Robotics: Future Research Directions; Report from the 2023 Workshop on Software Engineering for Robotics</t>
+  </si>
+  <si>
+    <t>Robots are experiencing a revolution as they permeate many aspects of our daily lives, from performing house maintenance to infrastructure inspection, from efficiently warehousing goods to autonomous vehicles, and more. This technical progress and its impact are astounding. This revolution, however, is outstripping the capabilities of existing software development processes, techniques, and tools, which largely have remained unchanged for decades. These capabilities are ill-suited to handling the challenges unique to robotics software such as dealing with a wide diversity of domains, heterogeneous hardware, programmed and learned components, complex physical environments captured and modeled with uncertainty, emergent behaviors that include human interactions, and scalability demands that span across multiple dimensions. Looking ahead to the need to develop software for robots that are ever more ubiquitous, autonomous, and reliant on complex adaptive components, hardware, and data, motivated an NSF-sponsored community workshop on the subject of Software Engineering for Robotics, held in Detroit, Michigan in October 2023. The goal of the workshop was to bring together thought leaders across robotics and software engineering to coalesce a community, and identify key problems in the area of SE for robotics that that community should aim to solve over the next 5 years. This report serves to summarize the motivation, activities, and findings of that workshop, in particular by articulating the challenges unique to robot software, and identifying a vision for fruitful near-term research directions to tackle them.</t>
+  </si>
+  <si>
+    <t>Emotion Classification In Software Engineering Texts: A Comparative Analysis of Pre-trained Transformers Language Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emotion recognition in software engineering texts is critical for understanding developer expressions and improving collaboration. This paper presents a comparative analysis of state-of-the-art Pre-trained Language Models (PTMs) for fine-grained emotion classification on two benchmark datasets from GitHub and Stack Overflow. We evaluate six transformer models - BERT, RoBERTa, ALBERT, DeBERTa, CodeBERT and GraphCodeBERT against the current best-performing tool SEntiMoji. Our analysis reveals consistent improvements ranging from 1.17% to 16.79% in terms of macro-averaged and micro-averaged F1 scores, with general domain models outperforming specialized ones. To further enhance PTMs, we incorporate polarity features in attention layer during training, demonstrating additional average gains of 1.0\% to 10.23\% over baseline PTMs approaches. Our work provides strong evidence for the advancements afforded by PTMs in recognizing nuanced emotions like Anger, Love, Fear, Joy, Sadness, and Surprise in software engineering contexts. Through comprehensive benchmarking and error analysis, we also outline scope for improvements to address contextual gaps.</t>
+  </si>
+  <si>
+    <t>Hidden Populations in Software Engineering: Challenges, Lessons Learned, and Opportunities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The growing emphasis on studying equity, diversity, and inclusion within software engineering has amplified the need to explore hidden populations within this field. Exploring hidden populations becomes important to obtain invaluable insights into the experiences, challenges, and perspectives of underrepresented groups in software engineering and, therefore, devise strategies to make the software industry more diverse. However, studying these hidden populations presents multifaceted challenges, including the complexities associated with identifying and engaging participants due to their marginalized status. In this paper, we discuss our experiences and lessons learned while conducting multiple studies involving hidden populations in software engineering. We emphasize the importance of recognizing and addressing these challenges within the software engineering research community to foster a more inclusive and comprehensive understanding of diverse populations of software professionals. </t>
+  </si>
+  <si>
+    <t>Towards Engineering Fair and Equitable Software Systems for Managing Low-Altitude Airspace Authorizations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Unmanned Aircraft Systems (sUAS) have gained widespread adoption across a diverse range of applications. This has introduced operational complexities within shared airspaces and an increase in reported incidents, raising safety concerns. In response, the U.S. Federal Aviation Administration (FAA) is developing a UAS Traffic Management (UTM) system to control access to airspace based on an sUAS's predicted ability to safely complete its mission. However, a fully automated system capable of swiftly approving or denying flight requests can be prone to bias and must consider safety, transparency, and fairness to diverse stakeholders. In this paper, we present an initial study that explores stakeholders' perspectives on factors that should be considered in an automated system. Results indicate flight characteristics and environmental conditions were perceived as most important but pilot and drone capabilities should also be considered. Further, several respondents indicated an aversion to any AI-supported automation, highlighting the need for full transparency in automated decision-making. Results provide a societal perspective on the challenges of automating UTM flight authorization decisions and help frame the ongoing design of a solution acceptable to the broader sUAS community. </t>
+  </si>
+  <si>
+    <t>Challenges, Adaptations, and Fringe Benefits of Conducting Software Engineering Research with Human Participants during the COVID-19 Pandemic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The COVID-19 pandemic changed the way we live, work and the way we conduct research. With the restrictions of lockdowns and social distancing, various impacts were experienced by many software engineering researchers, especially whose studies depend on human participants. We conducted a mixed methods study to understand the extent of this impact. Through a detailed survey with 89 software engineering researchers working with human participants around the world and a further nine follow-up interviews, we identified the key challenges faced, the adaptations made, and the surprising fringe benefits of conducting research involving human participants during the pandemic. Our findings also revealed that in retrospect, many researchers did not wish to revert to the old ways of conducting human-oriented research. Based on our analysis and insights, we share recommendations on how to conduct remote studies with human participants effectively in an increasingly hybrid world when face-to-face engagement is not possible or where remote participation is preferred. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1677,10 +2607,41 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF2D2D2D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF287916"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1704,11 +2665,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2024,3028 +2988,5730 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FD70CA-E905-4537-B47D-B2866D0AC99C}">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="F21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="F22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="F26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="F30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="F31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="F32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="F33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="F34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="F36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="F37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="F38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="F40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="F41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="F42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="F43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="F44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="F45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="F46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="F47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="F48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F49" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="F49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="F50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F51" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="F51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="F52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F53" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="F53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D54" t="s">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F54" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="F54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="F55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="F55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="F56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="F57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="F57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="F58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="F59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="F60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="F61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="F62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="F63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="F64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="F65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="F65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="F66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="F67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="F67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="F68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="F69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="F70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="F70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E71" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72">
+      <c r="F71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73">
+      <c r="F72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E73" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="F73" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74">
+      <c r="F73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E74" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
+      <c r="F74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F75" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76">
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F76" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
+      <c r="F76" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F77" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
+      <c r="F77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="F78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F79" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
+      <c r="F79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E80" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="F80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="F80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="F81" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="F81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F82" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="F82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F83" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="F83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F84" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="F84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E85" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F85" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="F85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="F86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="F86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F87" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="4">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F88" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
+      <c r="F88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F89" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
+      <c r="F89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="4">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E90" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F90" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
+      <c r="F90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E91" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F91" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="F91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F92" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="F92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F93" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
+      <c r="F93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F94" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
+      <c r="F94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F95" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="F95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F96" t="s">
-        <v>10</v>
-      </c>
+      <c r="F96" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="F97" t="s">
-        <v>10</v>
-      </c>
+      <c r="F97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="4"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98">
+      <c r="A98" s="4">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F98" t="s">
-        <v>10</v>
-      </c>
+      <c r="F98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="4"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="F99" t="s">
-        <v>10</v>
-      </c>
+      <c r="F99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100">
+      <c r="A100" s="4">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="F100" t="s">
-        <v>10</v>
-      </c>
+      <c r="F100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="4"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="F101" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="2" t="s">
+      <c r="F101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="5" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="F102" t="s">
-        <v>10</v>
-      </c>
+      <c r="F102" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="4"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E103" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F103" t="s">
-        <v>10</v>
-      </c>
+      <c r="F103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" s="4"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104">
+      <c r="A104" s="4">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E104" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="F104" t="s">
-        <v>10</v>
-      </c>
+      <c r="F104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="4"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F105" t="s">
-        <v>10</v>
-      </c>
+      <c r="F105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" s="4"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106">
+      <c r="A106" s="4">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E106" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F106" t="s">
-        <v>10</v>
-      </c>
+      <c r="F106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="4"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107">
+      <c r="A107" s="4">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E107" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="F107" t="s">
-        <v>10</v>
-      </c>
+      <c r="F107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="4"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108">
+      <c r="A108" s="4">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E108" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F108" t="s">
-        <v>10</v>
-      </c>
+      <c r="F108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="4"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="F109" t="s">
-        <v>10</v>
-      </c>
+      <c r="F109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="4"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110">
+      <c r="A110" s="4">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="F110" t="s">
-        <v>10</v>
-      </c>
+      <c r="F110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G110" s="4"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111">
+      <c r="A111" s="4">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="F111" t="s">
-        <v>10</v>
-      </c>
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112">
+      <c r="A112" s="4">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D112" t="s">
+      <c r="C112" s="4"/>
+      <c r="D112" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="F112" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113">
+      <c r="F112" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="F113" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114">
+      <c r="F113" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E114" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="F114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115">
+      <c r="F114" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="F115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116">
+      <c r="F115" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="E116" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="F116" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117">
+      <c r="F116" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" s="4"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E117" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="F117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118">
+      <c r="F117" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="F118" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119">
+      <c r="F118" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="E119" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="F119" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120">
+      <c r="F119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="E120" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="F120" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
+      <c r="F120" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E121" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="F121" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122">
+      <c r="F121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E122" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F122" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123">
+      <c r="F122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E123" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124">
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E124" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="F124" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125">
+      <c r="F124" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="F125" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126">
+      <c r="F125" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="F126" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127">
+      <c r="F126" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="F127" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128">
+      <c r="F127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="4"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="E128" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F128" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129">
+      <c r="F128" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F129" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130">
+      <c r="F129" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="F130" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131">
+      <c r="F130" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="4"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E131" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="F131" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132">
+      <c r="F131" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="4"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E132" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="F132" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133">
+      <c r="F132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="4"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="F133" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134">
+      <c r="F133" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" s="4"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="E134" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="F134" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135">
+      <c r="F134" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="4"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="E135" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="F135" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136">
+      <c r="F135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="F136" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137">
+      <c r="F136" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="4"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E137" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F137" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138">
+      <c r="F137" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="4"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="F138" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139">
+      <c r="F138" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="4"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E139" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F139" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140">
+      <c r="F139" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="4"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="D140" s="4"/>
+      <c r="E140" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="F140" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141">
+      <c r="F140" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="4"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E141" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="F141" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142">
+      <c r="F141" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" s="4"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="E142" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F142" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143">
+      <c r="F142" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" s="4"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
         <v>142</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="E143" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="F143" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144">
+      <c r="F143" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" s="4"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="4">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="F144" t="s">
-        <v>10</v>
-      </c>
+      <c r="F144" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" s="4"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145">
+      <c r="A145" s="4">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="E145" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="F145" t="s">
-        <v>10</v>
-      </c>
+      <c r="F145" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" s="4"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146">
+      <c r="A146" s="4">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E146" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="F146" t="s">
-        <v>10</v>
-      </c>
+      <c r="F146" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="4"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147">
+      <c r="A147" s="4">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F147" t="s">
-        <v>10</v>
-      </c>
+      <c r="F147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="4"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148">
+      <c r="A148" s="4">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="E148" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F148" t="s">
-        <v>10</v>
-      </c>
+      <c r="F148" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="4"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149">
+      <c r="A149" s="4">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="E149" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="F149" t="s">
-        <v>10</v>
-      </c>
+      <c r="F149" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="4"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150">
+      <c r="A150" s="4">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="F150" t="s">
-        <v>10</v>
-      </c>
+      <c r="F150" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="4"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151">
+      <c r="A151" s="4">
         <v>150</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="E151" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="F151" t="s">
-        <v>10</v>
-      </c>
-      <c r="G151" s="2" t="s">
+      <c r="F151" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="5" t="s">
         <v>537</v>
       </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="4"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="4"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" s="4"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="4"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="4"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" s="4"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" s="4"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="4"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="4"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="4">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="4"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="4">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="4"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="4">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="4"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="4">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" s="4"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="4">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="4"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="4">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" s="4"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="4">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="4"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="4">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="4"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="4"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G170" s="4"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="4">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="4"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="4">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" s="4"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="4">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" s="4"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="4">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" s="4"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="4">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" s="4"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="4">
+        <v>175</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" s="4"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="4">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" s="4"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="4">
+        <v>177</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="4"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="4">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="4"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="4">
+        <v>179</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" s="4"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="4">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="4"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="4">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="4"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="4">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="4">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="4"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="4">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" s="4"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="4">
+        <v>185</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="4"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="4">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="4"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="4">
+        <v>187</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="4"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="4">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="4"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="4">
+        <v>189</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="4"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="4">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" s="4"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="4">
+        <v>191</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="4"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="4">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="4"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="4">
+        <v>193</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="4"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="4">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="4"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="4">
+        <v>195</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="4"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="4">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" s="4"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="4">
+        <v>197</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="4"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="4">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="4"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="4">
+        <v>199</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="4"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="4">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="4"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="4">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="4"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="4">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D203" s="4"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="4"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="4">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D204" s="4"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="4"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="4">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="4"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="4">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D206" s="4"/>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="4"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="4">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="4"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="4">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="4"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209" s="4">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="4"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210" s="4">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="4"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211" s="4">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="4"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" s="4">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="4"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213" s="4">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="4"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214" s="4">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D214" s="4"/>
+      <c r="E214" s="4"/>
+      <c r="F214" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="4"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215" s="4">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="D215" s="4"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="4"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216" s="4">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="4"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" s="4">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="4"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218" s="4">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="4"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219" s="4">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D219" s="4"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="4"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A220" s="4">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="4"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" s="4">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="D221" s="4"/>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G221" s="4"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222" s="4">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="4"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" s="4">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" s="4"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" s="4">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="4"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" s="4">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D225" s="4"/>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="4"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226" s="4">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" s="4"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A227" s="4">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D227" s="4"/>
+      <c r="E227" s="4"/>
+      <c r="F227" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="4"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A228" s="4">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="4"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229" s="4">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D229" s="4"/>
+      <c r="E229" s="4"/>
+      <c r="F229" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="4"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A230" s="4">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="4"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A231" s="4">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D231" s="4"/>
+      <c r="E231" s="4"/>
+      <c r="F231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="4"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232" s="4">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D232" s="4"/>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="4"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" s="4">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D233" s="4"/>
+      <c r="E233" s="4"/>
+      <c r="F233" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" s="4"/>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234" s="4">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D234" s="4"/>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="4"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235" s="4">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="4"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A236" s="4">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
+      <c r="F236" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="4"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A237" s="4">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="4"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A238" s="4">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D238" s="4"/>
+      <c r="E238" s="4"/>
+      <c r="F238" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="4"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A239" s="4">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D239" s="4"/>
+      <c r="E239" s="4"/>
+      <c r="F239" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="4"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A240" s="4">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="4"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A241" s="4">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="D241" s="4"/>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="4"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A242" s="4">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="4"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A243" s="4">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D243" s="4"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="4"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A244" s="4">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="4"/>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A245" s="4">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="D245" s="4"/>
+      <c r="E245" s="4"/>
+      <c r="F245" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="4"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A246" s="4">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D246" s="4"/>
+      <c r="E246" s="4"/>
+      <c r="F246" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="4"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A247" s="4">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D247" s="4"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G247" s="4"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A248" s="4">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248" s="4"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A249" s="4">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D249" s="4"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G249" s="4"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A250" s="4">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D250" s="4"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="4"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A251" s="4">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="D251" s="4"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="4"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A252" s="4">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="D252" s="4"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G252" s="4"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A253" s="4">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="D253" s="4"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" s="4"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A254" s="4">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G254" s="4"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A255" s="4">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="D255" s="4"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G255" s="4"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A256" s="4">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D256" s="4"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="4"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A257" s="4">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="4"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A258" s="4">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="D258" s="4"/>
+      <c r="E258" s="4"/>
+      <c r="F258" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G258" s="4"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A259" s="4">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D259" s="4"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G259" s="4"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A260" s="4">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" s="4"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A261" s="4">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="D261" s="4"/>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G261" s="4"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A262" s="4">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="D262" s="4"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G262" s="4"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263" s="4">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="4"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A264" s="4">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G264" s="4"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265" s="4">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G265" s="4"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A266" s="4">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G266" s="4"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A267" s="4">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G267" s="4"/>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A268" s="4">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G268" s="4"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269" s="4">
+        <v>268</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G269" s="4"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A270" s="4">
+        <v>269</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G270" s="4"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A271" s="4">
+        <v>270</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G271" s="4"/>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A272" s="4">
+        <v>271</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D272" s="4"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G272" s="4"/>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" s="4">
+        <v>272</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G273" s="4"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A274" s="4">
+        <v>273</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D274" s="4"/>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G274" s="4"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A275" s="4">
+        <v>274</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="D275" s="4"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G275" s="4"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" s="4">
+        <v>275</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="D276" s="4"/>
+      <c r="E276" s="4"/>
+      <c r="F276" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G276" s="4"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A277" s="4">
+        <v>276</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="D277" s="4"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G277" s="4"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" s="4">
+        <v>277</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="D278" s="4"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G278" s="4"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A279" s="4">
+        <v>278</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="D279" s="4"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G279" s="4"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A280" s="4">
+        <v>279</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D280" s="4"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G280" s="4"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" s="4">
+        <v>280</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="D281" s="4"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G281" s="4"/>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A282" s="4">
+        <v>281</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="D282" s="4"/>
+      <c r="E282" s="4"/>
+      <c r="F282" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G282" s="4"/>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" s="4">
+        <v>282</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="4"/>
+      <c r="E283" s="4"/>
+      <c r="F283" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G283" s="4"/>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" s="4">
+        <v>283</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="D284" s="4"/>
+      <c r="E284" s="4"/>
+      <c r="F284" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G284" s="4"/>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" s="4">
+        <v>284</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="D285" s="4"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G285" s="4"/>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" s="4">
+        <v>285</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="D286" s="4"/>
+      <c r="E286" s="4"/>
+      <c r="F286" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G286" s="4"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A287" s="4">
+        <v>286</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="D287" s="4"/>
+      <c r="E287" s="4"/>
+      <c r="F287" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G287" s="4"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A288" s="4">
+        <v>287</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="D288" s="4"/>
+      <c r="E288" s="4"/>
+      <c r="F288" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G288" s="4"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" s="4">
+        <v>288</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D289" s="4"/>
+      <c r="E289" s="4"/>
+      <c r="F289" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G289" s="4"/>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" s="4">
+        <v>289</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="D290" s="4"/>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G290" s="4"/>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A291" s="4">
+        <v>290</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="D291" s="4"/>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G291" s="4"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A292" s="4">
+        <v>291</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="D292" s="4"/>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G292" s="4"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A293" s="4">
+        <v>292</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="D293" s="4"/>
+      <c r="E293" s="4"/>
+      <c r="F293" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G293" s="4"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A294" s="4">
+        <v>293</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D294" s="4"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G294" s="4"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A295" s="4">
+        <v>294</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="D295" s="4"/>
+      <c r="E295" s="4"/>
+      <c r="F295" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G295" s="4"/>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A296" s="4">
+        <v>295</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D296" s="4"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G296" s="4"/>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A297" s="4">
+        <v>296</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="D297" s="4"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G297" s="4"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A298" s="4">
+        <v>297</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="D298" s="4"/>
+      <c r="E298" s="4"/>
+      <c r="F298" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G298" s="4"/>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A299" s="4">
+        <v>298</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="D299" s="4"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G299" s="4"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A300" s="4">
+        <v>299</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D300" s="4"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G300" s="4"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A301" s="4">
+        <v>300</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="D301" s="4"/>
+      <c r="E301" s="4"/>
+      <c r="F301" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G301" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
